--- a/Versão5/ARQ/Ontologia_Ambientes.xlsx
+++ b/Versão5/ARQ/Ontologia_Ambientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ARQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBD76D8F-2298-4620-AF8C-36599DD78EA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4589A4C6-FAD8-4144-890D-A580CF8A6D45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3778" uniqueCount="923">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3798" uniqueCount="930">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -2840,6 +2840,27 @@
   </si>
   <si>
     <t>Código ABNT</t>
+  </si>
+  <si>
+    <t>De.API</t>
+  </si>
+  <si>
+    <t>Métodos</t>
+  </si>
+  <si>
+    <t>Macros</t>
+  </si>
+  <si>
+    <t>API.Revit</t>
+  </si>
+  <si>
+    <t>Aplicação Revit</t>
+  </si>
+  <si>
+    <t>Aplicativo Revit</t>
+  </si>
+  <si>
+    <t>Revit Aplication</t>
   </si>
 </sst>
 </file>
@@ -2930,7 +2951,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3057,6 +3078,12 @@
         <bgColor rgb="FFD9F2D0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFEF2CB"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="8">
     <border>
@@ -3157,7 +3184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3343,11 +3370,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="116">
+  <dxfs count="107">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3432,128 +3494,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3601,6 +3541,32 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -3846,14 +3812,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3901,6 +3859,14 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -5042,7 +5008,7 @@
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46253.633267245372</v>
+        <v>46258.592641550924</v>
       </c>
       <c r="C18" s="39" t="s">
         <v>171</v>
@@ -5147,7 +5113,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC181"/>
+  <dimension ref="A1:AC182"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.140625" style="52" bestFit="1" customWidth="1"/>
@@ -17374,7 +17340,7 @@
         <v>86</v>
       </c>
       <c r="X126" s="45" t="str">
-        <f t="shared" ref="X126:X181" si="36">CONCATENATE("Key-AMB-",A126)</f>
+        <f t="shared" ref="X126:X182" si="36">CONCATENATE("Key-AMB-",A126)</f>
         <v>Key-AMB-126</v>
       </c>
       <c r="Y126" s="30" t="s">
@@ -22694,7 +22660,7 @@
         <v>10</v>
       </c>
       <c r="T181" s="56" t="str">
-        <f t="shared" ref="T181:V181" si="78">SUBSTITUTE(C181, ".", " ")</f>
+        <f t="shared" ref="T181:V182" si="78">SUBSTITUTE(C181, ".", " ")</f>
         <v>De Arquitetura</v>
       </c>
       <c r="U181" s="56" t="str">
@@ -22728,293 +22694,343 @@
         <v>350</v>
       </c>
     </row>
+    <row r="182" spans="1:29" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A182" s="49">
+        <v>182</v>
+      </c>
+      <c r="B182" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="C182" s="65" t="s">
+        <v>923</v>
+      </c>
+      <c r="D182" s="65" t="s">
+        <v>924</v>
+      </c>
+      <c r="E182" s="65" t="s">
+        <v>925</v>
+      </c>
+      <c r="F182" s="65" t="s">
+        <v>926</v>
+      </c>
+      <c r="G182" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="H182" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="I182" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="J182" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="K182" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="L182" s="29" t="str">
+        <f t="shared" ref="L182:O182" si="79">SUBSTITUTE(CONCATENATE("", C182), ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="M182" s="29" t="str">
+        <f t="shared" si="79"/>
+        <v>Métodos</v>
+      </c>
+      <c r="N182" s="29" t="str">
+        <f t="shared" si="79"/>
+        <v>Macros</v>
+      </c>
+      <c r="O182" s="29" t="str">
+        <f t="shared" si="79"/>
+        <v>API Revit</v>
+      </c>
+      <c r="P182" s="30" t="s">
+        <v>927</v>
+      </c>
+      <c r="Q182" s="30" t="s">
+        <v>928</v>
+      </c>
+      <c r="R182" s="30" t="s">
+        <v>929</v>
+      </c>
+      <c r="S182" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="T182" s="30" t="str">
+        <f t="shared" si="78"/>
+        <v>De API</v>
+      </c>
+      <c r="U182" s="30" t="str">
+        <f t="shared" si="78"/>
+        <v>Métodos</v>
+      </c>
+      <c r="V182" s="56" t="str">
+        <f t="shared" si="78"/>
+        <v>Macros</v>
+      </c>
+      <c r="W182" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="X182" s="45" t="str">
+        <f t="shared" si="36"/>
+        <v>Key-AMB-182</v>
+      </c>
+      <c r="Y182" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z182" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA182" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB182" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC182" s="63" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="B2:B169 L22:P117 D49:F49 AD35:XFD117 AD165:XFD169 AD171:XFD172 AD174:XFD175 AD2:XFD9 AD179:XFD181 Y35:Y106 Y134:Y157 AA134:AA157 AA35:AA106 AC35:AC106 AC134:XFD157">
-    <cfRule type="cellIs" dxfId="115" priority="16" operator="equal">
+  <conditionalFormatting sqref="B170:D181">
+    <cfRule type="cellIs" dxfId="106" priority="60" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:F9 L2:P9">
-    <cfRule type="cellIs" dxfId="114" priority="49" operator="equal">
+    <cfRule type="cellIs" dxfId="105" priority="52" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D50:F73">
-    <cfRule type="cellIs" dxfId="113" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="104" priority="37" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D81:F86">
-    <cfRule type="cellIs" dxfId="112" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="103" priority="29" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D87:F100">
-    <cfRule type="cellIs" dxfId="111" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="102" priority="21" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E22:F28 D29:F48 D74:F80 E101:F117 D134:F157 A2:A181 AD22:XFD34 D101:D133 K157:P157">
-    <cfRule type="cellIs" dxfId="110" priority="151" operator="equal">
+  <conditionalFormatting sqref="E22:F28 D29:F48 D74:F80 E101:F117 D134:F157 D101:D133 K157:P157 A2:A182">
+    <cfRule type="cellIs" dxfId="101" priority="154" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E165:F169 L158:O164 L165:P169 Y29:Y34 Y107:Y133 AA107:AA133 AA29:AA34 AC107:AC133">
-    <cfRule type="cellIs" dxfId="109" priority="130" operator="equal">
+  <conditionalFormatting sqref="E165:F169 L158:O164 L165:P169">
+    <cfRule type="cellIs" dxfId="100" priority="133" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E171:F172">
-    <cfRule type="cellIs" dxfId="108" priority="67" operator="equal">
+    <cfRule type="cellIs" dxfId="99" priority="70" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F9">
-    <cfRule type="duplicateValues" dxfId="107" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="106" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="105" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="104" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="103" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F10:F21">
-    <cfRule type="duplicateValues" dxfId="102" priority="146"/>
-    <cfRule type="duplicateValues" dxfId="101" priority="147"/>
-    <cfRule type="duplicateValues" dxfId="100" priority="148"/>
-    <cfRule type="duplicateValues" dxfId="99" priority="149"/>
-    <cfRule type="duplicateValues" dxfId="98" priority="150"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="150"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="152"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="149"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F49:F67">
-    <cfRule type="duplicateValues" dxfId="97" priority="292"/>
-    <cfRule type="duplicateValues" dxfId="96" priority="294"/>
-    <cfRule type="duplicateValues" dxfId="95" priority="295"/>
-    <cfRule type="duplicateValues" dxfId="94" priority="296"/>
-    <cfRule type="duplicateValues" dxfId="93" priority="297"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="295"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="300"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="299"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="298"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="297"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F68:F73">
-    <cfRule type="duplicateValues" dxfId="92" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="91" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="90" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="89" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="88" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="87" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="86" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F74:F80 F22:F48 F101:F117">
-    <cfRule type="duplicateValues" dxfId="85" priority="264"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="265"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="266"/>
-    <cfRule type="duplicateValues" dxfId="82" priority="267"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="267"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="270"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="269"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="268"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F81:F86">
-    <cfRule type="duplicateValues" dxfId="81" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F87:F100">
-    <cfRule type="duplicateValues" dxfId="74" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F118:F133">
-    <cfRule type="duplicateValues" dxfId="67" priority="152"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="153"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="154"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="155"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="156"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="156"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="157"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="158"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="159"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F134:F157 F2:F48 F74:F80 F101:F117">
-    <cfRule type="duplicateValues" dxfId="62" priority="161"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="164"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F134:F157 F22:F48 F74:F80 F101:F117">
-    <cfRule type="duplicateValues" dxfId="61" priority="162"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="165"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F158:F164">
-    <cfRule type="duplicateValues" dxfId="60" priority="139"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="140"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="141"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="142"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="143"/>
-    <cfRule type="containsText" dxfId="55" priority="144" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="51" priority="147" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",F158)))</formula>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="54" priority="145"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="146"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="144"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="142"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="145"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="143"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="148"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F165:F169">
-    <cfRule type="duplicateValues" dxfId="53" priority="117"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="118"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="119"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="120"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="121"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="120"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F173">
-    <cfRule type="duplicateValues" dxfId="47" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F174:F175 F171:F172">
-    <cfRule type="duplicateValues" dxfId="46" priority="193"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="194"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="195"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="198"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="197"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="196"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F176 F182:F1048576 F1:F48 F74:F80 F101:F170">
-    <cfRule type="duplicateValues" dxfId="43" priority="115"/>
+  <conditionalFormatting sqref="F176 F183:F1048576 F1:F48 F74:F80 F101:F170">
+    <cfRule type="duplicateValues" dxfId="34" priority="118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F177:F178 F180:F181">
-    <cfRule type="duplicateValues" dxfId="42" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="74"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F177:F178">
-    <cfRule type="cellIs" dxfId="39" priority="72" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="75" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F179">
-    <cfRule type="duplicateValues" dxfId="38" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="74"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F180:F181 E170 L170:Q181 T170:V181 E173 E174:F175 E176:E181 R165:R169 R171:R172 R174:R178">
-    <cfRule type="cellIs" dxfId="37" priority="112" operator="equal">
+  <conditionalFormatting sqref="F180:F181 E170 L170:Q181 T170:V181 E173 E174:F175 E176:E181">
+    <cfRule type="cellIs" dxfId="28" priority="115" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L134:P156">
-    <cfRule type="cellIs" dxfId="36" priority="113" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="116" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P21">
-    <cfRule type="cellIs" dxfId="35" priority="129" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="132" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P128:P133">
-    <cfRule type="duplicateValues" dxfId="34" priority="123"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="124"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="125"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="126"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="127"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="127"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="126"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="128"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="129"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="130"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y158:Y164">
-    <cfRule type="duplicateValues" dxfId="29" priority="132"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="133"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="134"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="135"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="136"/>
-    <cfRule type="containsText" dxfId="24" priority="137" operator="containsText" text="null">
-      <formula>NOT(ISERROR(SEARCH("null",Y158)))</formula>
-    </cfRule>
-    <cfRule type="duplicateValues" dxfId="23" priority="138"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y2:AA2 Y3:Y9 AA3:AA9 Z3:Z181 AB2:AB181">
-    <cfRule type="cellIs" dxfId="22" priority="48" operator="equal">
+  <conditionalFormatting sqref="R1:R181">
+    <cfRule type="cellIs" dxfId="20" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y176:Y179 AA176:AA179">
-    <cfRule type="cellIs" dxfId="21" priority="11" operator="equal">
+  <conditionalFormatting sqref="Y158:Y164">
+    <cfRule type="duplicateValues" dxfId="19" priority="141"/>
+    <cfRule type="containsText" dxfId="18" priority="140" operator="containsText" text="null">
+      <formula>NOT(ISERROR(SEARCH("null",Y158)))</formula>
+    </cfRule>
+    <cfRule type="duplicateValues" dxfId="17" priority="139"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="138"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="137"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="135"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y165:Y173">
+    <cfRule type="cellIs" dxfId="12" priority="80" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y165:Y173 AA165:AA173 AC165:AC173">
-    <cfRule type="cellIs" dxfId="20" priority="77" operator="equal">
+  <conditionalFormatting sqref="Y175:Y179 AA175:AA179">
+    <cfRule type="cellIs" dxfId="11" priority="14" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y175 AA175 AC175">
-    <cfRule type="cellIs" dxfId="19" priority="89" operator="equal">
+  <conditionalFormatting sqref="Y181 AA181">
+    <cfRule type="cellIs" dxfId="10" priority="59" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y181 AA181 AC181">
-    <cfRule type="cellIs" dxfId="18" priority="56" operator="equal">
+  <conditionalFormatting sqref="Y2:AA2 AB2:AB181 Y3:Y9 AA3:AA9 Z3:Z181">
+    <cfRule type="cellIs" dxfId="9" priority="51" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA21">
-    <cfRule type="cellIs" dxfId="17" priority="128" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="131" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA158:AA164 AC158:AC164">
-    <cfRule type="cellIs" dxfId="16" priority="131" operator="equal">
+  <conditionalFormatting sqref="AC2:AC133">
+    <cfRule type="cellIs" dxfId="7" priority="17" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC2:AC34">
-    <cfRule type="cellIs" dxfId="15" priority="14" operator="equal">
+  <conditionalFormatting sqref="AC158:AC181">
+    <cfRule type="cellIs" dxfId="6" priority="16" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC174">
-    <cfRule type="cellIs" dxfId="14" priority="68" operator="equal">
+  <conditionalFormatting sqref="AD2:XFD9 B2:B169 L22:P117 AD22:XFD117 Y29:Y157 AA29:AA173 D49:F49 AC134:XFD157 AD165:XFD169 AD171:XFD172 AD174:XFD175 AD179:XFD181">
+    <cfRule type="cellIs" dxfId="5" priority="19" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC176:AC180">
-    <cfRule type="cellIs" dxfId="13" priority="13" operator="equal">
+  <conditionalFormatting sqref="B182">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B170:D181">
-    <cfRule type="cellIs" dxfId="12" priority="57" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
+  <conditionalFormatting sqref="F182">
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R35:R106">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R107:R117">
-    <cfRule type="cellIs" dxfId="10" priority="10" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R118:R133">
-    <cfRule type="cellIs" dxfId="9" priority="8" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R9">
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R134:R157">
-    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R158:R164">
-    <cfRule type="cellIs" dxfId="6" priority="9" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R1 R10:R34">
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R170">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R173">
-    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R179:R181">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+  <conditionalFormatting sqref="R182">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23218,7 +23234,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23347,7 +23363,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="51"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Versão5/ARQ/Ontologia_Ambientes.xlsx
+++ b/Versão5/ARQ/Ontologia_Ambientes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ARQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4589A4C6-FAD8-4144-890D-A580CF8A6D45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4CC4DBA-82E1-4B1E-9934-FC73CF0B1AA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -3383,33 +3383,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="107">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="106">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3636,14 +3610,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3672,23 +3638,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -4340,6 +4294,44 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i/>
         <strike val="0"/>
@@ -4805,15 +4797,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" style="62" customWidth="1"/>
-    <col min="2" max="2" width="51.42578125" style="62" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="40" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.28515625" style="62"/>
+    <col min="1" max="1" width="9.3046875" style="62" customWidth="1"/>
+    <col min="2" max="2" width="51.3828125" style="62" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="40" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.3046875" style="62"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="14" t="s">
         <v>46</v>
       </c>
@@ -4824,7 +4816,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="15" t="s">
         <v>48</v>
       </c>
@@ -4835,7 +4827,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="15" t="s">
         <v>50</v>
       </c>
@@ -4846,7 +4838,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="16" t="s">
         <v>51</v>
       </c>
@@ -4857,7 +4849,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="16" t="s">
         <v>52</v>
       </c>
@@ -4869,7 +4861,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="16" t="s">
         <v>53</v>
       </c>
@@ -4881,7 +4873,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="16" t="s">
         <v>54</v>
       </c>
@@ -4892,7 +4884,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="16" t="s">
         <v>56</v>
       </c>
@@ -4903,7 +4895,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="16" t="s">
         <v>57</v>
       </c>
@@ -4914,7 +4906,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="16" t="s">
         <v>59</v>
       </c>
@@ -4925,7 +4917,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="16" t="s">
         <v>61</v>
       </c>
@@ -4936,7 +4928,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="16" t="s">
         <v>62</v>
       </c>
@@ -4947,7 +4939,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="16" t="s">
         <v>63</v>
       </c>
@@ -4958,7 +4950,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="16" t="s">
         <v>64</v>
       </c>
@@ -4969,7 +4961,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="16" t="s">
         <v>65</v>
       </c>
@@ -4980,7 +4972,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="16" t="s">
         <v>66</v>
       </c>
@@ -4991,7 +4983,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="16" t="s">
         <v>67</v>
       </c>
@@ -5002,19 +4994,19 @@
         <v>171</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="16" t="s">
         <v>68</v>
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46258.592641550924</v>
+        <v>46264.563198148149</v>
       </c>
       <c r="C18" s="39" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="16" t="s">
         <v>174</v>
       </c>
@@ -5025,7 +5017,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="16" t="s">
         <v>175</v>
       </c>
@@ -5037,7 +5029,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="16" t="s">
         <v>176</v>
       </c>
@@ -5049,7 +5041,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="16" t="s">
         <v>69</v>
       </c>
@@ -5060,7 +5052,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="16" t="s">
         <v>70</v>
       </c>
@@ -5071,7 +5063,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="16" t="s">
         <v>71</v>
       </c>
@@ -5082,7 +5074,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="16" t="s">
         <v>72</v>
       </c>
@@ -5093,7 +5085,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="16" t="s">
         <v>169</v>
       </c>
@@ -5114,38 +5106,38 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AC182"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.140625" style="52" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" style="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" style="36" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="36" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" style="36" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="36" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="8.5703125" style="36" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="70.140625" style="36" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.85546875" style="36" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="36" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.7109375" style="36" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.5703125" style="36" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="127.28515625" style="36" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="135.28515625" style="36" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="106.140625" style="36" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.15234375" style="52" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.3046875" style="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.84375" style="36" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.3828125" style="36" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.69140625" style="36" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.3046875" style="36" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="8.53515625" style="36" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="70.15234375" style="36" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.84375" style="36" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.3828125" style="36" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.69140625" style="36" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.53515625" style="36" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="127.3046875" style="36" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="135.3046875" style="36" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="106.15234375" style="36" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="8" style="58" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.85546875" style="36" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="36" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.7109375" style="36" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.85546875" style="36" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.42578125" style="50" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.84375" style="36" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.3828125" style="36" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.69140625" style="36" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.84375" style="36" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.3828125" style="50" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="36" style="50" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.85546875" style="50" customWidth="1"/>
-    <col min="27" max="27" width="18.7109375" style="50" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.85546875" style="50" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15.85546875" style="61" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="36"/>
+    <col min="26" max="26" width="7.84375" style="50" customWidth="1"/>
+    <col min="27" max="27" width="18.69140625" style="50" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.84375" style="50" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15.84375" style="61" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.15234375" style="36"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="24" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" s="24" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="51">
         <v>0</v>
       </c>
@@ -5234,7 +5226,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="2" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="49">
         <v>2</v>
       </c>
@@ -5331,7 +5323,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="49">
         <v>3</v>
       </c>
@@ -5428,7 +5420,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="49">
         <v>4</v>
       </c>
@@ -5525,7 +5517,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="49">
         <v>5</v>
       </c>
@@ -5622,7 +5614,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="49">
         <v>6</v>
       </c>
@@ -5719,7 +5711,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="49">
         <v>7</v>
       </c>
@@ -5816,7 +5808,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="49">
         <v>8</v>
       </c>
@@ -5913,7 +5905,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="49">
         <v>9</v>
       </c>
@@ -6010,7 +6002,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="49">
         <v>10</v>
       </c>
@@ -6107,7 +6099,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="11" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="49">
         <v>11</v>
       </c>
@@ -6204,7 +6196,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="12" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="49">
         <v>12</v>
       </c>
@@ -6301,7 +6293,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="13" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="49">
         <v>13</v>
       </c>
@@ -6398,7 +6390,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="14" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="49">
         <v>14</v>
       </c>
@@ -6495,7 +6487,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="15" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="49">
         <v>15</v>
       </c>
@@ -6592,7 +6584,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="16" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="49">
         <v>16</v>
       </c>
@@ -6689,7 +6681,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="17" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="49">
         <v>17</v>
       </c>
@@ -6786,7 +6778,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="18" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="49">
         <v>18</v>
       </c>
@@ -6883,7 +6875,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="19" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="49">
         <v>19</v>
       </c>
@@ -6980,7 +6972,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="20" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="49">
         <v>20</v>
       </c>
@@ -7077,7 +7069,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="21" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="49">
         <v>21</v>
       </c>
@@ -7174,7 +7166,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="22" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="49">
         <v>22</v>
       </c>
@@ -7271,7 +7263,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="23" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="49">
         <v>23</v>
       </c>
@@ -7368,7 +7360,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="24" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="49">
         <v>24</v>
       </c>
@@ -7465,7 +7457,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="25" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="49">
         <v>25</v>
       </c>
@@ -7562,7 +7554,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="26" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="49">
         <v>26</v>
       </c>
@@ -7659,7 +7651,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="27" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="49">
         <v>27</v>
       </c>
@@ -7756,7 +7748,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="28" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="49">
         <v>28</v>
       </c>
@@ -7853,7 +7845,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="29" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="49">
         <v>29</v>
       </c>
@@ -7950,7 +7942,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="49">
         <v>30</v>
       </c>
@@ -8047,7 +8039,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="49">
         <v>31</v>
       </c>
@@ -8144,7 +8136,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="49">
         <v>32</v>
       </c>
@@ -8241,7 +8233,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="49">
         <v>33</v>
       </c>
@@ -8338,7 +8330,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="49">
         <v>34</v>
       </c>
@@ -8435,7 +8427,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="49">
         <v>35</v>
       </c>
@@ -8532,7 +8524,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="36" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="49">
         <v>36</v>
       </c>
@@ -8629,7 +8621,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="37" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="49">
         <v>37</v>
       </c>
@@ -8726,7 +8718,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="38" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="49">
         <v>38</v>
       </c>
@@ -8823,7 +8815,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="39" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="49">
         <v>39</v>
       </c>
@@ -8920,7 +8912,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="40" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="49">
         <v>40</v>
       </c>
@@ -9017,7 +9009,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="41" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="49">
         <v>41</v>
       </c>
@@ -9114,7 +9106,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="42" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="49">
         <v>42</v>
       </c>
@@ -9211,7 +9203,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="43" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="49">
         <v>43</v>
       </c>
@@ -9308,7 +9300,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="44" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="49">
         <v>44</v>
       </c>
@@ -9405,7 +9397,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="45" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="49">
         <v>45</v>
       </c>
@@ -9502,7 +9494,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="46" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="49">
         <v>46</v>
       </c>
@@ -9599,7 +9591,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="47" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="49">
         <v>47</v>
       </c>
@@ -9696,7 +9688,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="48" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="49">
         <v>48</v>
       </c>
@@ -9793,7 +9785,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="49" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="49">
         <v>49</v>
       </c>
@@ -9890,7 +9882,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="50" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="49">
         <v>50</v>
       </c>
@@ -9987,7 +9979,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="51" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="49">
         <v>51</v>
       </c>
@@ -10084,7 +10076,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="52" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="49">
         <v>52</v>
       </c>
@@ -10181,7 +10173,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="53" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="49">
         <v>53</v>
       </c>
@@ -10278,7 +10270,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="54" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="49">
         <v>54</v>
       </c>
@@ -10375,7 +10367,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="55" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="49">
         <v>55</v>
       </c>
@@ -10472,7 +10464,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="56" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="49">
         <v>56</v>
       </c>
@@ -10569,7 +10561,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="57" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="49">
         <v>57</v>
       </c>
@@ -10666,7 +10658,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="58" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="49">
         <v>58</v>
       </c>
@@ -10763,7 +10755,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="59" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="49">
         <v>59</v>
       </c>
@@ -10860,7 +10852,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="60" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="49">
         <v>60</v>
       </c>
@@ -10957,7 +10949,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="61" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="49">
         <v>61</v>
       </c>
@@ -11054,7 +11046,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="62" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="49">
         <v>62</v>
       </c>
@@ -11151,7 +11143,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="63" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="49">
         <v>63</v>
       </c>
@@ -11248,7 +11240,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="64" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="49">
         <v>64</v>
       </c>
@@ -11345,7 +11337,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="65" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="49">
         <v>65</v>
       </c>
@@ -11442,7 +11434,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="66" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="49">
         <v>66</v>
       </c>
@@ -11539,7 +11531,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="67" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="49">
         <v>67</v>
       </c>
@@ -11636,7 +11628,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="68" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="49">
         <v>68</v>
       </c>
@@ -11733,7 +11725,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="69" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="49">
         <v>69</v>
       </c>
@@ -11830,7 +11822,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="70" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="49">
         <v>70</v>
       </c>
@@ -11927,7 +11919,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="71" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="49">
         <v>71</v>
       </c>
@@ -12024,7 +12016,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="72" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="49">
         <v>72</v>
       </c>
@@ -12121,7 +12113,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="73" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="49">
         <v>73</v>
       </c>
@@ -12218,7 +12210,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="74" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="49">
         <v>74</v>
       </c>
@@ -12315,7 +12307,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="75" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="49">
         <v>75</v>
       </c>
@@ -12412,7 +12404,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="76" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="49">
         <v>76</v>
       </c>
@@ -12509,7 +12501,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="77" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="49">
         <v>77</v>
       </c>
@@ -12606,7 +12598,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="78" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="49">
         <v>78</v>
       </c>
@@ -12703,7 +12695,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="79" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="49">
         <v>79</v>
       </c>
@@ -12800,7 +12792,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="80" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="49">
         <v>80</v>
       </c>
@@ -12897,7 +12889,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="81" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="49">
         <v>81</v>
       </c>
@@ -12994,7 +12986,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="82" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="49">
         <v>82</v>
       </c>
@@ -13091,7 +13083,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="83" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="49">
         <v>83</v>
       </c>
@@ -13188,7 +13180,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="84" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="49">
         <v>84</v>
       </c>
@@ -13285,7 +13277,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="85" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="49">
         <v>85</v>
       </c>
@@ -13382,7 +13374,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="86" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="49">
         <v>86</v>
       </c>
@@ -13479,7 +13471,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="87" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="49">
         <v>87</v>
       </c>
@@ -13576,7 +13568,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="88" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="49">
         <v>88</v>
       </c>
@@ -13673,7 +13665,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="89" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="49">
         <v>89</v>
       </c>
@@ -13770,7 +13762,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="90" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="49">
         <v>90</v>
       </c>
@@ -13867,7 +13859,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="91" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="49">
         <v>91</v>
       </c>
@@ -13964,7 +13956,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="92" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="49">
         <v>92</v>
       </c>
@@ -14061,7 +14053,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="93" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="49">
         <v>93</v>
       </c>
@@ -14158,7 +14150,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="94" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="49">
         <v>94</v>
       </c>
@@ -14255,7 +14247,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="95" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="49">
         <v>95</v>
       </c>
@@ -14352,7 +14344,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="96" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="49">
         <v>96</v>
       </c>
@@ -14449,7 +14441,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="97" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="49">
         <v>97</v>
       </c>
@@ -14546,7 +14538,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="98" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="49">
         <v>98</v>
       </c>
@@ -14643,7 +14635,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="99" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="49">
         <v>99</v>
       </c>
@@ -14740,7 +14732,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="100" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="49">
         <v>100</v>
       </c>
@@ -14837,7 +14829,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="101" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="49">
         <v>101</v>
       </c>
@@ -14934,7 +14926,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="102" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="49">
         <v>102</v>
       </c>
@@ -15031,7 +15023,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="103" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="49">
         <v>103</v>
       </c>
@@ -15128,7 +15120,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="104" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="49">
         <v>104</v>
       </c>
@@ -15225,7 +15217,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="105" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="49">
         <v>105</v>
       </c>
@@ -15322,7 +15314,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="106" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="49">
         <v>106</v>
       </c>
@@ -15419,7 +15411,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="107" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="49">
         <v>107</v>
       </c>
@@ -15516,7 +15508,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="108" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="49">
         <v>108</v>
       </c>
@@ -15613,7 +15605,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="109" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="49">
         <v>109</v>
       </c>
@@ -15710,7 +15702,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="110" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="49">
         <v>110</v>
       </c>
@@ -15807,7 +15799,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="111" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="49">
         <v>111</v>
       </c>
@@ -15904,7 +15896,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="112" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="49">
         <v>112</v>
       </c>
@@ -16001,7 +15993,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="113" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="49">
         <v>113</v>
       </c>
@@ -16098,7 +16090,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="114" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="49">
         <v>114</v>
       </c>
@@ -16195,7 +16187,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="115" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="49">
         <v>115</v>
       </c>
@@ -16292,7 +16284,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="116" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="49">
         <v>116</v>
       </c>
@@ -16389,7 +16381,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="117" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="49">
         <v>117</v>
       </c>
@@ -16486,7 +16478,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="118" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="49">
         <v>118</v>
       </c>
@@ -16583,7 +16575,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="119" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="49">
         <v>119</v>
       </c>
@@ -16680,7 +16672,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="120" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="49">
         <v>120</v>
       </c>
@@ -16777,7 +16769,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="121" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="49">
         <v>121</v>
       </c>
@@ -16874,7 +16866,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="122" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="49">
         <v>122</v>
       </c>
@@ -16971,7 +16963,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="123" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="49">
         <v>123</v>
       </c>
@@ -17068,7 +17060,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="124" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="49">
         <v>124</v>
       </c>
@@ -17165,7 +17157,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="125" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="49">
         <v>125</v>
       </c>
@@ -17262,7 +17254,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="126" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="49">
         <v>126</v>
       </c>
@@ -17359,7 +17351,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="127" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="49">
         <v>127</v>
       </c>
@@ -17456,7 +17448,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="128" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="49">
         <v>128</v>
       </c>
@@ -17553,7 +17545,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="129" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="49">
         <v>129</v>
       </c>
@@ -17650,7 +17642,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="130" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="49">
         <v>130</v>
       </c>
@@ -17747,7 +17739,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="131" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="49">
         <v>131</v>
       </c>
@@ -17844,7 +17836,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="132" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="49">
         <v>132</v>
       </c>
@@ -17941,7 +17933,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="133" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133" s="49">
         <v>133</v>
       </c>
@@ -18038,7 +18030,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="134" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A134" s="49">
         <v>134</v>
       </c>
@@ -18135,7 +18127,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="135" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A135" s="49">
         <v>135</v>
       </c>
@@ -18232,7 +18224,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="136" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A136" s="49">
         <v>136</v>
       </c>
@@ -18329,7 +18321,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="137" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A137" s="49">
         <v>137</v>
       </c>
@@ -18426,7 +18418,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="138" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A138" s="49">
         <v>138</v>
       </c>
@@ -18523,7 +18515,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="139" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A139" s="49">
         <v>139</v>
       </c>
@@ -18620,7 +18612,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="140" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A140" s="49">
         <v>140</v>
       </c>
@@ -18717,7 +18709,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="141" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A141" s="49">
         <v>141</v>
       </c>
@@ -18814,7 +18806,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="142" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A142" s="49">
         <v>142</v>
       </c>
@@ -18911,7 +18903,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="143" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A143" s="49">
         <v>143</v>
       </c>
@@ -19008,7 +19000,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="144" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A144" s="49">
         <v>144</v>
       </c>
@@ -19105,7 +19097,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="145" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A145" s="49">
         <v>145</v>
       </c>
@@ -19202,7 +19194,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="146" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A146" s="49">
         <v>146</v>
       </c>
@@ -19299,7 +19291,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="147" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A147" s="49">
         <v>147</v>
       </c>
@@ -19396,7 +19388,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="148" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A148" s="49">
         <v>148</v>
       </c>
@@ -19493,7 +19485,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="149" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A149" s="49">
         <v>149</v>
       </c>
@@ -19590,7 +19582,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="150" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A150" s="49">
         <v>150</v>
       </c>
@@ -19687,7 +19679,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="151" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A151" s="49">
         <v>151</v>
       </c>
@@ -19784,7 +19776,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="152" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A152" s="49">
         <v>152</v>
       </c>
@@ -19881,7 +19873,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="153" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A153" s="49">
         <v>153</v>
       </c>
@@ -19978,7 +19970,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="154" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A154" s="49">
         <v>154</v>
       </c>
@@ -20075,7 +20067,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="155" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A155" s="49">
         <v>155</v>
       </c>
@@ -20172,7 +20164,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="156" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A156" s="49">
         <v>156</v>
       </c>
@@ -20269,7 +20261,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="157" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A157" s="49">
         <v>157</v>
       </c>
@@ -20366,7 +20358,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="158" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A158" s="49">
         <v>158</v>
       </c>
@@ -20463,7 +20455,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="159" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A159" s="49">
         <v>159</v>
       </c>
@@ -20560,7 +20552,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="160" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A160" s="49">
         <v>160</v>
       </c>
@@ -20657,7 +20649,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="161" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A161" s="49">
         <v>161</v>
       </c>
@@ -20754,7 +20746,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="162" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A162" s="49">
         <v>162</v>
       </c>
@@ -20851,7 +20843,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="163" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A163" s="49">
         <v>163</v>
       </c>
@@ -20948,7 +20940,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="164" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A164" s="49">
         <v>164</v>
       </c>
@@ -21045,7 +21037,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="165" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A165" s="49">
         <v>165</v>
       </c>
@@ -21142,7 +21134,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="166" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A166" s="49">
         <v>166</v>
       </c>
@@ -21239,7 +21231,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="167" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A167" s="49">
         <v>167</v>
       </c>
@@ -21336,7 +21328,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="168" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A168" s="49">
         <v>168</v>
       </c>
@@ -21433,7 +21425,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="169" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A169" s="49">
         <v>169</v>
       </c>
@@ -21530,7 +21522,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="170" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A170" s="49">
         <v>170</v>
       </c>
@@ -21627,7 +21619,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="171" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A171" s="49">
         <v>171</v>
       </c>
@@ -21724,7 +21716,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="172" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A172" s="49">
         <v>172</v>
       </c>
@@ -21821,7 +21813,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="173" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A173" s="49">
         <v>173</v>
       </c>
@@ -21918,7 +21910,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="174" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A174" s="49">
         <v>174</v>
       </c>
@@ -22015,7 +22007,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="175" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A175" s="49">
         <v>175</v>
       </c>
@@ -22112,7 +22104,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="176" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A176" s="49">
         <v>176</v>
       </c>
@@ -22209,7 +22201,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="177" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A177" s="49">
         <v>177</v>
       </c>
@@ -22306,7 +22298,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="178" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A178" s="49">
         <v>178</v>
       </c>
@@ -22403,7 +22395,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="179" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A179" s="49">
         <v>179</v>
       </c>
@@ -22500,7 +22492,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="180" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A180" s="49">
         <v>180</v>
       </c>
@@ -22597,7 +22589,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="181" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A181" s="49">
         <v>181</v>
       </c>
@@ -22694,7 +22686,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="182" spans="1:29" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:29" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="49">
         <v>182</v>
       </c>
@@ -22705,10 +22697,10 @@
         <v>923</v>
       </c>
       <c r="D182" s="65" t="s">
+        <v>925</v>
+      </c>
+      <c r="E182" s="65" t="s">
         <v>924</v>
-      </c>
-      <c r="E182" s="65" t="s">
-        <v>925</v>
       </c>
       <c r="F182" s="65" t="s">
         <v>926</v>
@@ -22734,11 +22726,11 @@
       </c>
       <c r="M182" s="29" t="str">
         <f t="shared" si="79"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="N182" s="29" t="str">
         <f t="shared" si="79"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="O182" s="29" t="str">
         <f t="shared" si="79"/>
@@ -22762,11 +22754,11 @@
       </c>
       <c r="U182" s="30" t="str">
         <f t="shared" si="78"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="V182" s="56" t="str">
         <f t="shared" si="78"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="W182" s="30" t="s">
         <v>86</v>
@@ -22793,244 +22785,239 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="B182">
+    <cfRule type="cellIs" dxfId="105" priority="2" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B170:D181">
-    <cfRule type="cellIs" dxfId="106" priority="60" operator="equal">
+    <cfRule type="cellIs" dxfId="104" priority="60" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:F9 L2:P9">
-    <cfRule type="cellIs" dxfId="105" priority="52" operator="equal">
+    <cfRule type="cellIs" dxfId="103" priority="52" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D50:F73">
-    <cfRule type="cellIs" dxfId="104" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="102" priority="37" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D81:F86">
-    <cfRule type="cellIs" dxfId="103" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="101" priority="29" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D87:F100">
-    <cfRule type="cellIs" dxfId="102" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="100" priority="21" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E22:F28 D29:F48 D74:F80 E101:F117 D134:F157 D101:D133 K157:P157 A2:A182">
-    <cfRule type="cellIs" dxfId="101" priority="154" operator="equal">
+  <conditionalFormatting sqref="E22:F28 D29:F48 D74:F80 E101:F117 D134:F157 A2:A182 D101:D133 K157:P157">
+    <cfRule type="cellIs" dxfId="99" priority="154" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E165:F169 L158:O164 L165:P169">
-    <cfRule type="cellIs" dxfId="100" priority="133" operator="equal">
+    <cfRule type="cellIs" dxfId="98" priority="133" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E171:F172">
-    <cfRule type="cellIs" dxfId="99" priority="70" operator="equal">
+    <cfRule type="cellIs" dxfId="97" priority="70" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F9">
-    <cfRule type="duplicateValues" dxfId="98" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="97" priority="54"/>
     <cfRule type="duplicateValues" dxfId="96" priority="53"/>
     <cfRule type="duplicateValues" dxfId="95" priority="57"/>
     <cfRule type="duplicateValues" dxfId="94" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F10:F21">
-    <cfRule type="duplicateValues" dxfId="93" priority="150"/>
-    <cfRule type="duplicateValues" dxfId="92" priority="153"/>
     <cfRule type="duplicateValues" dxfId="91" priority="152"/>
-    <cfRule type="duplicateValues" dxfId="90" priority="151"/>
-    <cfRule type="duplicateValues" dxfId="89" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="150"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="153"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F49:F67">
-    <cfRule type="duplicateValues" dxfId="88" priority="295"/>
-    <cfRule type="duplicateValues" dxfId="87" priority="300"/>
-    <cfRule type="duplicateValues" dxfId="86" priority="299"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="298"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="297"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="297"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="295"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="299"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="298"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="300"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F68:F73">
-    <cfRule type="duplicateValues" dxfId="83" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="82" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F74:F80 F22:F48 F101:F117">
-    <cfRule type="duplicateValues" dxfId="76" priority="267"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="270"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="269"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="270"/>
     <cfRule type="duplicateValues" dxfId="73" priority="268"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="267"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="269"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F81:F86">
-    <cfRule type="duplicateValues" dxfId="72" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F87:F100">
-    <cfRule type="duplicateValues" dxfId="65" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F118:F133">
-    <cfRule type="duplicateValues" dxfId="58" priority="155"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="156"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="157"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="158"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="159"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="158"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="159"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="157"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="156"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="155"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F134:F157 F2:F48 F74:F80 F101:F117">
-    <cfRule type="duplicateValues" dxfId="53" priority="164"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="164"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F134:F157 F22:F48 F74:F80 F101:F117">
-    <cfRule type="duplicateValues" dxfId="52" priority="165"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="165"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F158:F164">
-    <cfRule type="containsText" dxfId="51" priority="147" operator="containsText" text="null">
+    <cfRule type="duplicateValues" dxfId="49" priority="143"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="144"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="145"/>
+    <cfRule type="containsText" dxfId="46" priority="147" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",F158)))</formula>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="50" priority="146"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="144"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="142"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="145"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="143"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="148"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="146"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="148"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="142"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F165:F169">
-    <cfRule type="duplicateValues" dxfId="44" priority="122"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="123"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="124"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="125"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="121"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="120"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F173">
-    <cfRule type="duplicateValues" dxfId="38" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F174:F175 F171:F172">
-    <cfRule type="duplicateValues" dxfId="37" priority="198"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="197"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="196"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="198"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="197"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="196"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F176 F183:F1048576 F1:F48 F74:F80 F101:F170">
-    <cfRule type="duplicateValues" dxfId="34" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F177:F178 F180:F181">
-    <cfRule type="duplicateValues" dxfId="33" priority="78"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="76"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F177:F178">
-    <cfRule type="cellIs" dxfId="30" priority="75" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="75" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F179">
-    <cfRule type="duplicateValues" dxfId="29" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F180:F181 E170 L170:Q181 T170:V181 E173 E174:F175 E176:E181">
-    <cfRule type="cellIs" dxfId="28" priority="115" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="115" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F182">
+    <cfRule type="duplicateValues" dxfId="25" priority="3"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L134:P156">
-    <cfRule type="cellIs" dxfId="27" priority="116" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="116" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P21">
-    <cfRule type="cellIs" dxfId="26" priority="132" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="132" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P128:P133">
-    <cfRule type="duplicateValues" dxfId="25" priority="127"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="126"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="128"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="129"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="130"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="126"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="127"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="128"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="130"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="129"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R181">
-    <cfRule type="cellIs" dxfId="20" priority="4" operator="equal">
+  <conditionalFormatting sqref="R1:R182">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y158:Y164">
-    <cfRule type="duplicateValues" dxfId="19" priority="141"/>
-    <cfRule type="containsText" dxfId="18" priority="140" operator="containsText" text="null">
+    <cfRule type="duplicateValues" dxfId="16" priority="141"/>
+    <cfRule type="containsText" dxfId="15" priority="140" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",Y158)))</formula>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="17" priority="139"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="138"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="137"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="136"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="135"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="139"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="138"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="137"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="135"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y165:Y173">
-    <cfRule type="cellIs" dxfId="12" priority="80" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="80" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y175:Y179 AA175:AA179">
-    <cfRule type="cellIs" dxfId="11" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="14" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y181 AA181">
-    <cfRule type="cellIs" dxfId="10" priority="59" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="59" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:AA2 AB2:AB181 Y3:Y9 AA3:AA9 Z3:Z181">
-    <cfRule type="cellIs" dxfId="9" priority="51" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="51" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA21">
-    <cfRule type="cellIs" dxfId="8" priority="131" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="131" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2:AC133">
-    <cfRule type="cellIs" dxfId="7" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="17" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC158:AC181">
-    <cfRule type="cellIs" dxfId="6" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="16" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2:XFD9 B2:B169 L22:P117 AD22:XFD117 Y29:Y157 AA29:AA173 D49:F49 AC134:XFD157 AD165:XFD169 AD171:XFD172 AD174:XFD175 AD179:XFD181">
-    <cfRule type="cellIs" dxfId="5" priority="19" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B182">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F182">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R182">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="19" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23043,15 +23030,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.28515625" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="10" width="5.140625" style="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="21" width="5.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="8"/>
+    <col min="1" max="1" width="1.3046875" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="10" width="5.15234375" style="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="21" width="5.53515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="15.45" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>12</v>
       </c>
@@ -23116,7 +23103,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -23191,14 +23178,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B299E44-CC41-4C47-93B0-FF411236635D}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="8.5" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="1.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="3.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.3828125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.69140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="6.69140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="11">
         <v>1</v>
       </c>
@@ -23215,7 +23202,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="8.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="22">
         <v>2</v>
       </c>
@@ -23234,7 +23221,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23246,27 +23233,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96F4F343-F8A9-4565-8E75-460BD2B52D7E}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="7.35" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="7.4" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="55" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.5703125" style="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" style="34" customWidth="1"/>
-    <col min="4" max="4" width="2.42578125" style="34" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="1.85546875" style="34" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="2.42578125" style="34" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="1.85546875" style="34" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="2.42578125" style="34" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="1.85546875" style="34" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="2.5703125" style="34" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.85546875" style="34" customWidth="1"/>
-    <col min="12" max="12" width="2.42578125" style="34" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4.5703125" style="34" customWidth="1"/>
-    <col min="14" max="14" width="4.140625" style="34" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.140625" style="34" customWidth="1"/>
-    <col min="16" max="16384" width="9.28515625" style="34"/>
+    <col min="1" max="1" width="1.69140625" style="55" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.53515625" style="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.3046875" style="34" customWidth="1"/>
+    <col min="4" max="4" width="2.3828125" style="34" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="1.84375" style="34" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="2.3828125" style="34" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="1.84375" style="34" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="2.3828125" style="34" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="1.84375" style="34" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="2.53515625" style="34" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.84375" style="34" customWidth="1"/>
+    <col min="12" max="12" width="2.3828125" style="34" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.53515625" style="34" customWidth="1"/>
+    <col min="14" max="14" width="4.15234375" style="34" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.15234375" style="34" customWidth="1"/>
+    <col min="16" max="16384" width="9.3046875" style="34"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="20.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="20.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="53" t="s">
         <v>11</v>
       </c>
@@ -23313,7 +23300,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="54">
         <v>2</v>
       </c>
@@ -23363,7 +23350,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="51"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Versão5/ARQ/Ontologia_Ambientes.xlsx
+++ b/Versão5/ARQ/Ontologia_Ambientes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ARQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4CC4DBA-82E1-4B1E-9934-FC73CF0B1AA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3176EF3-E449-4E98-A271-49461CE53A98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3798" uniqueCount="930">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3878" uniqueCount="946">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -2830,9 +2830,6 @@
     <t>Nuevo compartimento</t>
   </si>
   <si>
-    <t>[ - ]</t>
-  </si>
-  <si>
     <t>Parâmetro Rvt</t>
   </si>
   <si>
@@ -2851,16 +2848,67 @@
     <t>Macros</t>
   </si>
   <si>
-    <t>API.Revit</t>
-  </si>
-  <si>
-    <t>Aplicação Revit</t>
-  </si>
-  <si>
-    <t>Aplicativo Revit</t>
-  </si>
-  <si>
-    <t>Revit Aplication</t>
+    <t>Função.Auxiliar</t>
+  </si>
+  <si>
+    <t>Define uma Função Auxiliar (helper) numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol de ayudante en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Helper Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Global</t>
+  </si>
+  <si>
+    <t>Define uma Função Global numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol global en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Global Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Local</t>
+  </si>
+  <si>
+    <t>Define uma Função Local numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol local en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Local Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Filtro</t>
+  </si>
+  <si>
+    <t>Define uma Função para filtrar objetos numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina una función para filtrar objetos en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Function to filter objects in an application</t>
+  </si>
+  <si>
+    <t>Códigos.Visuais</t>
+  </si>
+  <si>
+    <t>Bloco.de.Código</t>
+  </si>
+  <si>
+    <t>Define um Código escrito em sistemas de programação visual</t>
+  </si>
+  <si>
+    <t>Define un código escrito en sistemas de programación visual</t>
+  </si>
+  <si>
+    <t>Defines a Code written in visual programming systems</t>
   </si>
 </sst>
 </file>
@@ -3383,7 +3431,15 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="106">
+  <dxfs count="323">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3396,78 +3452,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color rgb="FFFFFFFF"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3478,6 +3462,78 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3518,14 +3574,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3554,6 +3602,14 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3594,22 +3650,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3628,6 +3668,14 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3656,6 +3704,14 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3816,14 +3872,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3834,6 +3882,14 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -4324,11 +4380,2071 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i/>
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -4797,15 +6913,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.3046875" style="62" customWidth="1"/>
-    <col min="2" max="2" width="51.3828125" style="62" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="40" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.3046875" style="62"/>
+    <col min="1" max="1" width="9.28515625" style="62" customWidth="1"/>
+    <col min="2" max="2" width="51.42578125" style="62" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="40" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.28515625" style="62"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>46</v>
       </c>
@@ -4816,7 +6932,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
         <v>48</v>
       </c>
@@ -4827,7 +6943,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
         <v>50</v>
       </c>
@@ -4838,7 +6954,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
         <v>51</v>
       </c>
@@ -4849,7 +6965,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
         <v>52</v>
       </c>
@@ -4861,7 +6977,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>53</v>
       </c>
@@ -4873,7 +6989,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>54</v>
       </c>
@@ -4884,7 +7000,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>56</v>
       </c>
@@ -4895,7 +7011,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>57</v>
       </c>
@@ -4906,7 +7022,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>59</v>
       </c>
@@ -4917,7 +7033,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>61</v>
       </c>
@@ -4928,7 +7044,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
         <v>62</v>
       </c>
@@ -4939,7 +7055,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
         <v>63</v>
       </c>
@@ -4950,7 +7066,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
         <v>64</v>
       </c>
@@ -4961,7 +7077,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
         <v>65</v>
       </c>
@@ -4972,7 +7088,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
         <v>66</v>
       </c>
@@ -4983,7 +7099,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>67</v>
       </c>
@@ -4994,19 +7110,19 @@
         <v>171</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
         <v>68</v>
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46264.563198148149</v>
+        <v>46268.51108877315</v>
       </c>
       <c r="C18" s="39" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
         <v>174</v>
       </c>
@@ -5017,7 +7133,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
         <v>175</v>
       </c>
@@ -5029,7 +7145,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>176</v>
       </c>
@@ -5041,7 +7157,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
         <v>69</v>
       </c>
@@ -5052,7 +7168,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
         <v>70</v>
       </c>
@@ -5063,7 +7179,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
         <v>71</v>
       </c>
@@ -5074,7 +7190,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
         <v>72</v>
       </c>
@@ -5085,7 +7201,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
         <v>169</v>
       </c>
@@ -5105,39 +7221,39 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC182"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AC186"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.15234375" style="52" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.3046875" style="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.84375" style="36" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.3828125" style="36" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.69140625" style="36" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.3046875" style="36" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="8.53515625" style="36" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="70.15234375" style="36" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.84375" style="36" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.3828125" style="36" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.69140625" style="36" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.53515625" style="36" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="127.3046875" style="36" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="135.3046875" style="36" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="106.15234375" style="36" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" style="52" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" style="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" style="36" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="36" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" style="36" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="36" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="8.5703125" style="36" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="70.140625" style="36" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.85546875" style="36" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="36" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.7109375" style="36" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.5703125" style="36" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="127.28515625" style="36" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="135.28515625" style="36" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="106.140625" style="36" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="8" style="58" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.84375" style="36" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.3828125" style="36" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.69140625" style="36" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.84375" style="36" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.3828125" style="50" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.85546875" style="36" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="36" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.7109375" style="36" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.85546875" style="36" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.42578125" style="50" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="36" style="50" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.84375" style="50" customWidth="1"/>
-    <col min="27" max="27" width="18.69140625" style="50" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.84375" style="50" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15.84375" style="61" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.15234375" style="36"/>
+    <col min="26" max="26" width="7.85546875" style="50" customWidth="1"/>
+    <col min="27" max="27" width="23.7109375" style="50" customWidth="1"/>
+    <col min="28" max="28" width="6.85546875" style="50" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15.85546875" style="61" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="36"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="24" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:29" s="24" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="51">
         <v>0</v>
       </c>
@@ -5214,19 +7330,19 @@
         <v>81</v>
       </c>
       <c r="Z1" s="26" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="AA1" s="26" t="s">
         <v>82</v>
       </c>
       <c r="AB1" s="26" t="s">
+        <v>920</v>
+      </c>
+      <c r="AC1" s="59" t="s">
         <v>921</v>
       </c>
-      <c r="AC1" s="59" t="s">
-        <v>922</v>
-      </c>
     </row>
-    <row r="2" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="49">
         <v>2</v>
       </c>
@@ -5310,20 +7426,20 @@
       <c r="Y2" s="30" t="s">
         <v>217</v>
       </c>
-      <c r="Z2" s="30" t="s">
-        <v>919</v>
+      <c r="Z2" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA2" s="41" t="s">
         <v>192</v>
       </c>
-      <c r="AB2" s="30" t="s">
-        <v>919</v>
+      <c r="AB2" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC2" s="56" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="49">
         <v>3</v>
       </c>
@@ -5407,20 +7523,20 @@
       <c r="Y3" s="30" t="s">
         <v>217</v>
       </c>
-      <c r="Z3" s="30" t="s">
-        <v>919</v>
+      <c r="Z3" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA3" s="41" t="s">
         <v>193</v>
       </c>
-      <c r="AB3" s="30" t="s">
-        <v>919</v>
+      <c r="AB3" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC3" s="56" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="49">
         <v>4</v>
       </c>
@@ -5504,20 +7620,20 @@
       <c r="Y4" s="30" t="s">
         <v>217</v>
       </c>
-      <c r="Z4" s="30" t="s">
-        <v>919</v>
+      <c r="Z4" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA4" s="41" t="s">
         <v>194</v>
       </c>
-      <c r="AB4" s="30" t="s">
-        <v>919</v>
+      <c r="AB4" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC4" s="56" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="49">
         <v>5</v>
       </c>
@@ -5601,20 +7717,20 @@
       <c r="Y5" s="30" t="s">
         <v>217</v>
       </c>
-      <c r="Z5" s="30" t="s">
-        <v>919</v>
+      <c r="Z5" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA5" s="41" t="s">
         <v>195</v>
       </c>
-      <c r="AB5" s="30" t="s">
-        <v>919</v>
+      <c r="AB5" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC5" s="56" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="49">
         <v>6</v>
       </c>
@@ -5698,20 +7814,20 @@
       <c r="Y6" s="30" t="s">
         <v>217</v>
       </c>
-      <c r="Z6" s="30" t="s">
-        <v>919</v>
+      <c r="Z6" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA6" s="41" t="s">
         <v>196</v>
       </c>
-      <c r="AB6" s="30" t="s">
-        <v>919</v>
+      <c r="AB6" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC6" s="56" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="49">
         <v>7</v>
       </c>
@@ -5795,20 +7911,20 @@
       <c r="Y7" s="30" t="s">
         <v>217</v>
       </c>
-      <c r="Z7" s="30" t="s">
-        <v>919</v>
+      <c r="Z7" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA7" s="41" t="s">
         <v>196</v>
       </c>
-      <c r="AB7" s="30" t="s">
-        <v>919</v>
+      <c r="AB7" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC7" s="56" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="49">
         <v>8</v>
       </c>
@@ -5892,20 +8008,20 @@
       <c r="Y8" s="30" t="s">
         <v>217</v>
       </c>
-      <c r="Z8" s="30" t="s">
-        <v>919</v>
+      <c r="Z8" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA8" s="41" t="s">
         <v>192</v>
       </c>
-      <c r="AB8" s="30" t="s">
-        <v>919</v>
+      <c r="AB8" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC8" s="56" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="49">
         <v>9</v>
       </c>
@@ -5989,20 +8105,20 @@
       <c r="Y9" s="30" t="s">
         <v>217</v>
       </c>
-      <c r="Z9" s="30" t="s">
-        <v>919</v>
+      <c r="Z9" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA9" s="41" t="s">
         <v>192</v>
       </c>
-      <c r="AB9" s="30" t="s">
-        <v>919</v>
+      <c r="AB9" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC9" s="56" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="49">
         <v>10</v>
       </c>
@@ -6086,20 +8202,20 @@
       <c r="Y10" s="30" t="s">
         <v>553</v>
       </c>
-      <c r="Z10" s="30" t="s">
-        <v>919</v>
+      <c r="Z10" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA10" s="41" t="s">
         <v>191</v>
       </c>
-      <c r="AB10" s="30" t="s">
-        <v>919</v>
+      <c r="AB10" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC10" s="56" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="11" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="49">
         <v>11</v>
       </c>
@@ -6183,20 +8299,20 @@
       <c r="Y11" s="30" t="s">
         <v>553</v>
       </c>
-      <c r="Z11" s="30" t="s">
-        <v>919</v>
+      <c r="Z11" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA11" s="41" t="s">
         <v>191</v>
       </c>
-      <c r="AB11" s="30" t="s">
-        <v>919</v>
+      <c r="AB11" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC11" s="56" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="12" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="49">
         <v>12</v>
       </c>
@@ -6280,20 +8396,20 @@
       <c r="Y12" s="30" t="s">
         <v>553</v>
       </c>
-      <c r="Z12" s="30" t="s">
-        <v>919</v>
+      <c r="Z12" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA12" s="41" t="s">
         <v>191</v>
       </c>
-      <c r="AB12" s="30" t="s">
-        <v>919</v>
+      <c r="AB12" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC12" s="56" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="13" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="49">
         <v>13</v>
       </c>
@@ -6377,20 +8493,20 @@
       <c r="Y13" s="30" t="s">
         <v>553</v>
       </c>
-      <c r="Z13" s="30" t="s">
-        <v>919</v>
+      <c r="Z13" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA13" s="41" t="s">
         <v>191</v>
       </c>
-      <c r="AB13" s="30" t="s">
-        <v>919</v>
+      <c r="AB13" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC13" s="56" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="14" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="49">
         <v>14</v>
       </c>
@@ -6474,20 +8590,20 @@
       <c r="Y14" s="30" t="s">
         <v>553</v>
       </c>
-      <c r="Z14" s="30" t="s">
-        <v>919</v>
+      <c r="Z14" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA14" s="41" t="s">
         <v>191</v>
       </c>
-      <c r="AB14" s="30" t="s">
-        <v>919</v>
+      <c r="AB14" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC14" s="56" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="15" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="49">
         <v>15</v>
       </c>
@@ -6571,20 +8687,20 @@
       <c r="Y15" s="30" t="s">
         <v>553</v>
       </c>
-      <c r="Z15" s="30" t="s">
-        <v>919</v>
+      <c r="Z15" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA15" s="41" t="s">
         <v>191</v>
       </c>
-      <c r="AB15" s="30" t="s">
-        <v>919</v>
+      <c r="AB15" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC15" s="56" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="16" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="49">
         <v>16</v>
       </c>
@@ -6668,20 +8784,20 @@
       <c r="Y16" s="30" t="s">
         <v>553</v>
       </c>
-      <c r="Z16" s="30" t="s">
-        <v>919</v>
+      <c r="Z16" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA16" s="41" t="s">
         <v>191</v>
       </c>
-      <c r="AB16" s="30" t="s">
-        <v>919</v>
+      <c r="AB16" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC16" s="56" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="17" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="49">
         <v>17</v>
       </c>
@@ -6765,20 +8881,20 @@
       <c r="Y17" s="30" t="s">
         <v>553</v>
       </c>
-      <c r="Z17" s="30" t="s">
-        <v>919</v>
+      <c r="Z17" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA17" s="41" t="s">
         <v>191</v>
       </c>
-      <c r="AB17" s="30" t="s">
-        <v>919</v>
+      <c r="AB17" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC17" s="56" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="18" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="49">
         <v>18</v>
       </c>
@@ -6862,20 +8978,20 @@
       <c r="Y18" s="30" t="s">
         <v>553</v>
       </c>
-      <c r="Z18" s="30" t="s">
-        <v>919</v>
+      <c r="Z18" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA18" s="41" t="s">
         <v>191</v>
       </c>
-      <c r="AB18" s="30" t="s">
-        <v>919</v>
+      <c r="AB18" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC18" s="56" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="19" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="49">
         <v>19</v>
       </c>
@@ -6959,20 +9075,20 @@
       <c r="Y19" s="30" t="s">
         <v>553</v>
       </c>
-      <c r="Z19" s="30" t="s">
-        <v>919</v>
+      <c r="Z19" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA19" s="41" t="s">
         <v>191</v>
       </c>
-      <c r="AB19" s="30" t="s">
-        <v>919</v>
+      <c r="AB19" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC19" s="56" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="20" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="49">
         <v>20</v>
       </c>
@@ -7056,20 +9172,20 @@
       <c r="Y20" s="30" t="s">
         <v>553</v>
       </c>
-      <c r="Z20" s="30" t="s">
-        <v>919</v>
+      <c r="Z20" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA20" s="41" t="s">
         <v>191</v>
       </c>
-      <c r="AB20" s="30" t="s">
-        <v>919</v>
+      <c r="AB20" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC20" s="56" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="21" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="49">
         <v>21</v>
       </c>
@@ -7153,20 +9269,20 @@
       <c r="Y21" s="30" t="s">
         <v>553</v>
       </c>
-      <c r="Z21" s="30" t="s">
-        <v>919</v>
+      <c r="Z21" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA21" s="30" t="s">
         <v>243</v>
       </c>
-      <c r="AB21" s="30" t="s">
-        <v>919</v>
+      <c r="AB21" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC21" s="56" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="22" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="49">
         <v>22</v>
       </c>
@@ -7250,20 +9366,20 @@
       <c r="Y22" s="30" t="s">
         <v>553</v>
       </c>
-      <c r="Z22" s="30" t="s">
-        <v>919</v>
+      <c r="Z22" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA22" s="41" t="s">
         <v>191</v>
       </c>
-      <c r="AB22" s="30" t="s">
-        <v>919</v>
+      <c r="AB22" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC22" s="56" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="23" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="49">
         <v>23</v>
       </c>
@@ -7347,20 +9463,20 @@
       <c r="Y23" s="30" t="s">
         <v>553</v>
       </c>
-      <c r="Z23" s="30" t="s">
-        <v>919</v>
+      <c r="Z23" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA23" s="41" t="s">
         <v>191</v>
       </c>
-      <c r="AB23" s="30" t="s">
-        <v>919</v>
+      <c r="AB23" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC23" s="56" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="24" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="49">
         <v>24</v>
       </c>
@@ -7444,20 +9560,20 @@
       <c r="Y24" s="30" t="s">
         <v>553</v>
       </c>
-      <c r="Z24" s="30" t="s">
-        <v>919</v>
+      <c r="Z24" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA24" s="41" t="s">
         <v>191</v>
       </c>
-      <c r="AB24" s="30" t="s">
-        <v>919</v>
+      <c r="AB24" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC24" s="56" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="25" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="49">
         <v>25</v>
       </c>
@@ -7541,20 +9657,20 @@
       <c r="Y25" s="30" t="s">
         <v>553</v>
       </c>
-      <c r="Z25" s="30" t="s">
-        <v>919</v>
+      <c r="Z25" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA25" s="41" t="s">
         <v>191</v>
       </c>
-      <c r="AB25" s="30" t="s">
-        <v>919</v>
+      <c r="AB25" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC25" s="56" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="26" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="49">
         <v>26</v>
       </c>
@@ -7638,20 +9754,20 @@
       <c r="Y26" s="30" t="s">
         <v>553</v>
       </c>
-      <c r="Z26" s="30" t="s">
-        <v>919</v>
+      <c r="Z26" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA26" s="41" t="s">
         <v>191</v>
       </c>
-      <c r="AB26" s="30" t="s">
-        <v>919</v>
+      <c r="AB26" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC26" s="56" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="27" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="49">
         <v>27</v>
       </c>
@@ -7735,20 +9851,20 @@
       <c r="Y27" s="30" t="s">
         <v>553</v>
       </c>
-      <c r="Z27" s="30" t="s">
-        <v>919</v>
+      <c r="Z27" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA27" s="41" t="s">
         <v>191</v>
       </c>
-      <c r="AB27" s="30" t="s">
-        <v>919</v>
+      <c r="AB27" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC27" s="56" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="28" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="49">
         <v>28</v>
       </c>
@@ -7832,20 +9948,20 @@
       <c r="Y28" s="30" t="s">
         <v>553</v>
       </c>
-      <c r="Z28" s="30" t="s">
-        <v>919</v>
+      <c r="Z28" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA28" s="41" t="s">
         <v>191</v>
       </c>
-      <c r="AB28" s="30" t="s">
-        <v>919</v>
+      <c r="AB28" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC28" s="56" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="29" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="49">
         <v>29</v>
       </c>
@@ -7929,20 +10045,20 @@
       <c r="Y29" s="30" t="s">
         <v>554</v>
       </c>
-      <c r="Z29" s="30" t="s">
-        <v>919</v>
+      <c r="Z29" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA29" s="30" t="s">
         <v>243</v>
       </c>
-      <c r="AB29" s="30" t="s">
-        <v>919</v>
+      <c r="AB29" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC29" s="56" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="49">
         <v>30</v>
       </c>
@@ -8026,20 +10142,20 @@
       <c r="Y30" s="30" t="s">
         <v>554</v>
       </c>
-      <c r="Z30" s="30" t="s">
-        <v>919</v>
+      <c r="Z30" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA30" s="30" t="s">
         <v>243</v>
       </c>
-      <c r="AB30" s="30" t="s">
-        <v>919</v>
+      <c r="AB30" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC30" s="56" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="49">
         <v>31</v>
       </c>
@@ -8123,20 +10239,20 @@
       <c r="Y31" s="30" t="s">
         <v>554</v>
       </c>
-      <c r="Z31" s="30" t="s">
-        <v>919</v>
+      <c r="Z31" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA31" s="30" t="s">
         <v>243</v>
       </c>
-      <c r="AB31" s="30" t="s">
-        <v>919</v>
+      <c r="AB31" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC31" s="56" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="49">
         <v>32</v>
       </c>
@@ -8220,20 +10336,20 @@
       <c r="Y32" s="30" t="s">
         <v>554</v>
       </c>
-      <c r="Z32" s="30" t="s">
-        <v>919</v>
+      <c r="Z32" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA32" s="30" t="s">
         <v>243</v>
       </c>
-      <c r="AB32" s="30" t="s">
-        <v>919</v>
+      <c r="AB32" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC32" s="56" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="49">
         <v>33</v>
       </c>
@@ -8317,20 +10433,20 @@
       <c r="Y33" s="30" t="s">
         <v>554</v>
       </c>
-      <c r="Z33" s="30" t="s">
-        <v>919</v>
+      <c r="Z33" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA33" s="30" t="s">
         <v>243</v>
       </c>
-      <c r="AB33" s="30" t="s">
-        <v>919</v>
+      <c r="AB33" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC33" s="56" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="49">
         <v>34</v>
       </c>
@@ -8414,20 +10530,20 @@
       <c r="Y34" s="30" t="s">
         <v>216</v>
       </c>
-      <c r="Z34" s="30" t="s">
-        <v>919</v>
+      <c r="Z34" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA34" s="30" t="s">
         <v>243</v>
       </c>
-      <c r="AB34" s="30" t="s">
-        <v>919</v>
+      <c r="AB34" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC34" s="56" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="49">
         <v>35</v>
       </c>
@@ -8511,20 +10627,20 @@
       <c r="Y35" s="30" t="s">
         <v>218</v>
       </c>
-      <c r="Z35" s="30" t="s">
-        <v>919</v>
+      <c r="Z35" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA35" s="41" t="s">
         <v>197</v>
       </c>
-      <c r="AB35" s="30" t="s">
-        <v>919</v>
+      <c r="AB35" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC35" s="56" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="36" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="49">
         <v>36</v>
       </c>
@@ -8608,20 +10724,20 @@
       <c r="Y36" s="30" t="s">
         <v>218</v>
       </c>
-      <c r="Z36" s="30" t="s">
-        <v>919</v>
+      <c r="Z36" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA36" s="41" t="s">
         <v>197</v>
       </c>
-      <c r="AB36" s="30" t="s">
-        <v>919</v>
+      <c r="AB36" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC36" s="56" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="37" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="49">
         <v>37</v>
       </c>
@@ -8705,20 +10821,20 @@
       <c r="Y37" s="30" t="s">
         <v>218</v>
       </c>
-      <c r="Z37" s="30" t="s">
-        <v>919</v>
+      <c r="Z37" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA37" s="41" t="s">
         <v>197</v>
       </c>
-      <c r="AB37" s="30" t="s">
-        <v>919</v>
+      <c r="AB37" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC37" s="56" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="38" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="49">
         <v>38</v>
       </c>
@@ -8802,20 +10918,20 @@
       <c r="Y38" s="30" t="s">
         <v>218</v>
       </c>
-      <c r="Z38" s="30" t="s">
-        <v>919</v>
+      <c r="Z38" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA38" s="41" t="s">
         <v>198</v>
       </c>
-      <c r="AB38" s="30" t="s">
-        <v>919</v>
+      <c r="AB38" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC38" s="56" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="39" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="49">
         <v>39</v>
       </c>
@@ -8899,20 +11015,20 @@
       <c r="Y39" s="30" t="s">
         <v>218</v>
       </c>
-      <c r="Z39" s="30" t="s">
-        <v>919</v>
+      <c r="Z39" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA39" s="41" t="s">
         <v>197</v>
       </c>
-      <c r="AB39" s="30" t="s">
-        <v>919</v>
+      <c r="AB39" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC39" s="60" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="40" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="49">
         <v>40</v>
       </c>
@@ -8996,20 +11112,20 @@
       <c r="Y40" s="30" t="s">
         <v>218</v>
       </c>
-      <c r="Z40" s="30" t="s">
-        <v>919</v>
+      <c r="Z40" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA40" s="41" t="s">
         <v>197</v>
       </c>
-      <c r="AB40" s="30" t="s">
-        <v>919</v>
+      <c r="AB40" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC40" s="60" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="41" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="49">
         <v>41</v>
       </c>
@@ -9093,20 +11209,20 @@
       <c r="Y41" s="30" t="s">
         <v>218</v>
       </c>
-      <c r="Z41" s="30" t="s">
-        <v>919</v>
+      <c r="Z41" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA41" s="41" t="s">
         <v>199</v>
       </c>
-      <c r="AB41" s="30" t="s">
-        <v>919</v>
+      <c r="AB41" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC41" s="56" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="42" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="49">
         <v>42</v>
       </c>
@@ -9190,20 +11306,20 @@
       <c r="Y42" s="30" t="s">
         <v>218</v>
       </c>
-      <c r="Z42" s="30" t="s">
-        <v>919</v>
+      <c r="Z42" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA42" s="41" t="s">
         <v>201</v>
       </c>
-      <c r="AB42" s="30" t="s">
-        <v>919</v>
+      <c r="AB42" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC42" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="43" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="49">
         <v>43</v>
       </c>
@@ -9287,20 +11403,20 @@
       <c r="Y43" s="30" t="s">
         <v>218</v>
       </c>
-      <c r="Z43" s="30" t="s">
-        <v>919</v>
+      <c r="Z43" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA43" s="41" t="s">
         <v>200</v>
       </c>
-      <c r="AB43" s="30" t="s">
-        <v>919</v>
+      <c r="AB43" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC43" s="56" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="44" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="49">
         <v>44</v>
       </c>
@@ -9384,20 +11500,20 @@
       <c r="Y44" s="30" t="s">
         <v>218</v>
       </c>
-      <c r="Z44" s="30" t="s">
-        <v>919</v>
+      <c r="Z44" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA44" s="41" t="s">
         <v>201</v>
       </c>
-      <c r="AB44" s="30" t="s">
-        <v>919</v>
+      <c r="AB44" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC44" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="45" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="49">
         <v>45</v>
       </c>
@@ -9481,20 +11597,20 @@
       <c r="Y45" s="30" t="s">
         <v>218</v>
       </c>
-      <c r="Z45" s="30" t="s">
-        <v>919</v>
+      <c r="Z45" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA45" s="41" t="s">
         <v>201</v>
       </c>
-      <c r="AB45" s="30" t="s">
-        <v>919</v>
+      <c r="AB45" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC45" s="56" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="46" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="49">
         <v>46</v>
       </c>
@@ -9578,20 +11694,20 @@
       <c r="Y46" s="30" t="s">
         <v>218</v>
       </c>
-      <c r="Z46" s="30" t="s">
-        <v>919</v>
+      <c r="Z46" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA46" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="AB46" s="30" t="s">
-        <v>919</v>
+      <c r="AB46" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC46" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="47" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="49">
         <v>47</v>
       </c>
@@ -9675,20 +11791,20 @@
       <c r="Y47" s="30" t="s">
         <v>218</v>
       </c>
-      <c r="Z47" s="30" t="s">
-        <v>919</v>
+      <c r="Z47" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA47" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="AB47" s="30" t="s">
-        <v>919</v>
+      <c r="AB47" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC47" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="48" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="49">
         <v>48</v>
       </c>
@@ -9772,20 +11888,20 @@
       <c r="Y48" s="30" t="s">
         <v>218</v>
       </c>
-      <c r="Z48" s="30" t="s">
-        <v>919</v>
+      <c r="Z48" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA48" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="AB48" s="30" t="s">
-        <v>919</v>
+      <c r="AB48" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC48" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="49" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="49">
         <v>49</v>
       </c>
@@ -9869,20 +11985,20 @@
       <c r="Y49" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z49" s="30" t="s">
-        <v>919</v>
+      <c r="Z49" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA49" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB49" s="30" t="s">
-        <v>919</v>
+      <c r="AB49" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC49" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="50" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="49">
         <v>50</v>
       </c>
@@ -9966,20 +12082,20 @@
       <c r="Y50" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z50" s="30" t="s">
-        <v>919</v>
+      <c r="Z50" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA50" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB50" s="30" t="s">
-        <v>919</v>
+      <c r="AB50" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC50" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="51" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="49">
         <v>51</v>
       </c>
@@ -10063,20 +12179,20 @@
       <c r="Y51" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z51" s="30" t="s">
-        <v>919</v>
+      <c r="Z51" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA51" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB51" s="30" t="s">
-        <v>919</v>
+      <c r="AB51" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC51" s="56" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="52" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="49">
         <v>52</v>
       </c>
@@ -10160,20 +12276,20 @@
       <c r="Y52" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z52" s="30" t="s">
-        <v>919</v>
+      <c r="Z52" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA52" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB52" s="30" t="s">
-        <v>919</v>
+      <c r="AB52" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC52" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="53" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="49">
         <v>53</v>
       </c>
@@ -10257,20 +12373,20 @@
       <c r="Y53" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z53" s="30" t="s">
-        <v>919</v>
+      <c r="Z53" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA53" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB53" s="30" t="s">
-        <v>919</v>
+      <c r="AB53" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC53" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="54" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="49">
         <v>54</v>
       </c>
@@ -10354,20 +12470,20 @@
       <c r="Y54" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z54" s="30" t="s">
-        <v>919</v>
+      <c r="Z54" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA54" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB54" s="30" t="s">
-        <v>919</v>
+      <c r="AB54" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC54" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="55" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="49">
         <v>55</v>
       </c>
@@ -10451,20 +12567,20 @@
       <c r="Y55" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z55" s="30" t="s">
-        <v>919</v>
+      <c r="Z55" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA55" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB55" s="30" t="s">
-        <v>919</v>
+      <c r="AB55" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC55" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="56" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="49">
         <v>56</v>
       </c>
@@ -10548,20 +12664,20 @@
       <c r="Y56" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z56" s="30" t="s">
-        <v>919</v>
+      <c r="Z56" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA56" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB56" s="30" t="s">
-        <v>919</v>
+      <c r="AB56" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC56" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="57" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="49">
         <v>57</v>
       </c>
@@ -10645,20 +12761,20 @@
       <c r="Y57" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z57" s="30" t="s">
-        <v>919</v>
+      <c r="Z57" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA57" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB57" s="30" t="s">
-        <v>919</v>
+      <c r="AB57" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC57" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="58" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="49">
         <v>58</v>
       </c>
@@ -10742,20 +12858,20 @@
       <c r="Y58" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z58" s="30" t="s">
-        <v>919</v>
+      <c r="Z58" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA58" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB58" s="30" t="s">
-        <v>919</v>
+      <c r="AB58" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC58" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="59" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="49">
         <v>59</v>
       </c>
@@ -10839,20 +12955,20 @@
       <c r="Y59" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z59" s="30" t="s">
-        <v>919</v>
+      <c r="Z59" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA59" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB59" s="30" t="s">
-        <v>919</v>
+      <c r="AB59" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC59" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="60" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="49">
         <v>60</v>
       </c>
@@ -10936,20 +13052,20 @@
       <c r="Y60" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z60" s="30" t="s">
-        <v>919</v>
+      <c r="Z60" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA60" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB60" s="30" t="s">
-        <v>919</v>
+      <c r="AB60" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC60" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="61" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="49">
         <v>61</v>
       </c>
@@ -11033,20 +13149,20 @@
       <c r="Y61" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z61" s="30" t="s">
-        <v>919</v>
+      <c r="Z61" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA61" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB61" s="30" t="s">
-        <v>919</v>
+      <c r="AB61" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC61" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="62" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="49">
         <v>62</v>
       </c>
@@ -11130,20 +13246,20 @@
       <c r="Y62" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z62" s="30" t="s">
-        <v>919</v>
+      <c r="Z62" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA62" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB62" s="30" t="s">
-        <v>919</v>
+      <c r="AB62" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC62" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="63" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="49">
         <v>63</v>
       </c>
@@ -11227,20 +13343,20 @@
       <c r="Y63" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z63" s="30" t="s">
-        <v>919</v>
+      <c r="Z63" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA63" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB63" s="30" t="s">
-        <v>919</v>
+      <c r="AB63" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC63" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="64" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="49">
         <v>64</v>
       </c>
@@ -11324,20 +13440,20 @@
       <c r="Y64" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z64" s="30" t="s">
-        <v>919</v>
+      <c r="Z64" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA64" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB64" s="30" t="s">
-        <v>919</v>
+      <c r="AB64" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC64" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="65" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="49">
         <v>65</v>
       </c>
@@ -11421,20 +13537,20 @@
       <c r="Y65" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z65" s="30" t="s">
-        <v>919</v>
+      <c r="Z65" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA65" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB65" s="30" t="s">
-        <v>919</v>
+      <c r="AB65" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC65" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="66" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="49">
         <v>66</v>
       </c>
@@ -11518,20 +13634,20 @@
       <c r="Y66" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z66" s="30" t="s">
-        <v>919</v>
+      <c r="Z66" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA66" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB66" s="30" t="s">
-        <v>919</v>
+      <c r="AB66" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC66" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="67" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="49">
         <v>67</v>
       </c>
@@ -11615,20 +13731,20 @@
       <c r="Y67" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z67" s="30" t="s">
-        <v>919</v>
+      <c r="Z67" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA67" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB67" s="30" t="s">
-        <v>919</v>
+      <c r="AB67" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC67" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="68" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="49">
         <v>68</v>
       </c>
@@ -11712,20 +13828,20 @@
       <c r="Y68" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z68" s="30" t="s">
-        <v>919</v>
+      <c r="Z68" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA68" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB68" s="30" t="s">
-        <v>919</v>
+      <c r="AB68" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC68" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="69" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="49">
         <v>69</v>
       </c>
@@ -11809,20 +13925,20 @@
       <c r="Y69" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z69" s="30" t="s">
-        <v>919</v>
+      <c r="Z69" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA69" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB69" s="30" t="s">
-        <v>919</v>
+      <c r="AB69" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC69" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="70" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="49">
         <v>70</v>
       </c>
@@ -11906,20 +14022,20 @@
       <c r="Y70" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z70" s="30" t="s">
-        <v>919</v>
+      <c r="Z70" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA70" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB70" s="30" t="s">
-        <v>919</v>
+      <c r="AB70" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC70" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="71" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="49">
         <v>71</v>
       </c>
@@ -12003,20 +14119,20 @@
       <c r="Y71" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z71" s="30" t="s">
-        <v>919</v>
+      <c r="Z71" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA71" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB71" s="30" t="s">
-        <v>919</v>
+      <c r="AB71" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC71" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="72" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="49">
         <v>72</v>
       </c>
@@ -12100,20 +14216,20 @@
       <c r="Y72" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z72" s="30" t="s">
-        <v>919</v>
+      <c r="Z72" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA72" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB72" s="30" t="s">
-        <v>919</v>
+      <c r="AB72" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC72" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="73" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="49">
         <v>73</v>
       </c>
@@ -12197,20 +14313,20 @@
       <c r="Y73" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z73" s="30" t="s">
-        <v>919</v>
+      <c r="Z73" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA73" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB73" s="30" t="s">
-        <v>919</v>
+      <c r="AB73" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC73" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="74" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="49">
         <v>74</v>
       </c>
@@ -12294,20 +14410,20 @@
       <c r="Y74" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z74" s="30" t="s">
-        <v>919</v>
+      <c r="Z74" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA74" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB74" s="30" t="s">
-        <v>919</v>
+      <c r="AB74" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC74" s="56" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="75" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="49">
         <v>75</v>
       </c>
@@ -12391,20 +14507,20 @@
       <c r="Y75" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z75" s="30" t="s">
-        <v>919</v>
+      <c r="Z75" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA75" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB75" s="30" t="s">
-        <v>919</v>
+      <c r="AB75" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC75" s="56" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="76" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="49">
         <v>76</v>
       </c>
@@ -12488,20 +14604,20 @@
       <c r="Y76" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z76" s="30" t="s">
-        <v>919</v>
+      <c r="Z76" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA76" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB76" s="30" t="s">
-        <v>919</v>
+      <c r="AB76" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC76" s="56" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="77" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="49">
         <v>77</v>
       </c>
@@ -12585,20 +14701,20 @@
       <c r="Y77" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z77" s="30" t="s">
-        <v>919</v>
+      <c r="Z77" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA77" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB77" s="30" t="s">
-        <v>919</v>
+      <c r="AB77" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC77" s="56" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="78" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="49">
         <v>78</v>
       </c>
@@ -12682,20 +14798,20 @@
       <c r="Y78" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z78" s="30" t="s">
-        <v>919</v>
+      <c r="Z78" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA78" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB78" s="30" t="s">
-        <v>919</v>
+      <c r="AB78" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC78" s="56" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="79" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="49">
         <v>79</v>
       </c>
@@ -12779,20 +14895,20 @@
       <c r="Y79" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z79" s="30" t="s">
-        <v>919</v>
+      <c r="Z79" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA79" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB79" s="30" t="s">
-        <v>919</v>
+      <c r="AB79" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC79" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="80" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="49">
         <v>80</v>
       </c>
@@ -12876,20 +14992,20 @@
       <c r="Y80" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z80" s="30" t="s">
-        <v>919</v>
+      <c r="Z80" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA80" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB80" s="30" t="s">
-        <v>919</v>
+      <c r="AB80" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC80" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="81" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="49">
         <v>81</v>
       </c>
@@ -12973,20 +15089,20 @@
       <c r="Y81" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z81" s="30" t="s">
-        <v>919</v>
+      <c r="Z81" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA81" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB81" s="30" t="s">
-        <v>919</v>
+      <c r="AB81" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC81" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="82" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="49">
         <v>82</v>
       </c>
@@ -13070,20 +15186,20 @@
       <c r="Y82" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z82" s="30" t="s">
-        <v>919</v>
+      <c r="Z82" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA82" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB82" s="30" t="s">
-        <v>919</v>
+      <c r="AB82" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC82" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="83" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="49">
         <v>83</v>
       </c>
@@ -13167,20 +15283,20 @@
       <c r="Y83" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z83" s="30" t="s">
-        <v>919</v>
+      <c r="Z83" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA83" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB83" s="30" t="s">
-        <v>919</v>
+      <c r="AB83" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC83" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="84" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="49">
         <v>84</v>
       </c>
@@ -13264,20 +15380,20 @@
       <c r="Y84" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z84" s="30" t="s">
-        <v>919</v>
+      <c r="Z84" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA84" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB84" s="30" t="s">
-        <v>919</v>
+      <c r="AB84" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC84" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="85" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="49">
         <v>85</v>
       </c>
@@ -13361,20 +15477,20 @@
       <c r="Y85" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z85" s="30" t="s">
-        <v>919</v>
+      <c r="Z85" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA85" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB85" s="30" t="s">
-        <v>919</v>
+      <c r="AB85" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC85" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="86" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="49">
         <v>86</v>
       </c>
@@ -13458,20 +15574,20 @@
       <c r="Y86" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z86" s="30" t="s">
-        <v>919</v>
+      <c r="Z86" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA86" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB86" s="30" t="s">
-        <v>919</v>
+      <c r="AB86" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC86" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="87" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="49">
         <v>87</v>
       </c>
@@ -13555,20 +15671,20 @@
       <c r="Y87" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z87" s="30" t="s">
-        <v>919</v>
+      <c r="Z87" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA87" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB87" s="30" t="s">
-        <v>919</v>
+      <c r="AB87" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC87" s="56" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="88" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="49">
         <v>88</v>
       </c>
@@ -13652,20 +15768,20 @@
       <c r="Y88" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z88" s="30" t="s">
-        <v>919</v>
+      <c r="Z88" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA88" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB88" s="30" t="s">
-        <v>919</v>
+      <c r="AB88" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC88" s="56" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="89" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="49">
         <v>89</v>
       </c>
@@ -13749,20 +15865,20 @@
       <c r="Y89" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z89" s="30" t="s">
-        <v>919</v>
+      <c r="Z89" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA89" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB89" s="30" t="s">
-        <v>919</v>
+      <c r="AB89" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC89" s="56" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="90" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="49">
         <v>90</v>
       </c>
@@ -13846,20 +15962,20 @@
       <c r="Y90" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z90" s="30" t="s">
-        <v>919</v>
+      <c r="Z90" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA90" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB90" s="30" t="s">
-        <v>919</v>
+      <c r="AB90" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC90" s="56" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="91" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="49">
         <v>91</v>
       </c>
@@ -13943,20 +16059,20 @@
       <c r="Y91" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z91" s="30" t="s">
-        <v>919</v>
+      <c r="Z91" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA91" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB91" s="30" t="s">
-        <v>919</v>
+      <c r="AB91" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC91" s="56" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="92" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="49">
         <v>92</v>
       </c>
@@ -14040,20 +16156,20 @@
       <c r="Y92" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z92" s="30" t="s">
-        <v>919</v>
+      <c r="Z92" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA92" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB92" s="30" t="s">
-        <v>919</v>
+      <c r="AB92" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC92" s="56" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="93" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="49">
         <v>93</v>
       </c>
@@ -14137,20 +16253,20 @@
       <c r="Y93" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z93" s="30" t="s">
-        <v>919</v>
+      <c r="Z93" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA93" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB93" s="30" t="s">
-        <v>919</v>
+      <c r="AB93" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC93" s="56" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="94" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="49">
         <v>94</v>
       </c>
@@ -14234,20 +16350,20 @@
       <c r="Y94" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z94" s="30" t="s">
-        <v>919</v>
+      <c r="Z94" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA94" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB94" s="30" t="s">
-        <v>919</v>
+      <c r="AB94" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC94" s="56" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="95" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="49">
         <v>95</v>
       </c>
@@ -14331,20 +16447,20 @@
       <c r="Y95" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z95" s="30" t="s">
-        <v>919</v>
+      <c r="Z95" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA95" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB95" s="30" t="s">
-        <v>919</v>
+      <c r="AB95" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC95" s="56" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="96" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="49">
         <v>96</v>
       </c>
@@ -14428,20 +16544,20 @@
       <c r="Y96" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z96" s="30" t="s">
-        <v>919</v>
+      <c r="Z96" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA96" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB96" s="30" t="s">
-        <v>919</v>
+      <c r="AB96" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC96" s="56" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="97" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="49">
         <v>97</v>
       </c>
@@ -14525,20 +16641,20 @@
       <c r="Y97" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z97" s="30" t="s">
-        <v>919</v>
+      <c r="Z97" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA97" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB97" s="30" t="s">
-        <v>919</v>
+      <c r="AB97" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC97" s="56" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="98" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="49">
         <v>98</v>
       </c>
@@ -14622,20 +16738,20 @@
       <c r="Y98" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z98" s="30" t="s">
-        <v>919</v>
+      <c r="Z98" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA98" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB98" s="30" t="s">
-        <v>919</v>
+      <c r="AB98" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC98" s="56" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="99" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="49">
         <v>99</v>
       </c>
@@ -14719,20 +16835,20 @@
       <c r="Y99" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z99" s="30" t="s">
-        <v>919</v>
+      <c r="Z99" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA99" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB99" s="30" t="s">
-        <v>919</v>
+      <c r="AB99" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC99" s="56" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="100" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="49">
         <v>100</v>
       </c>
@@ -14816,20 +16932,20 @@
       <c r="Y100" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z100" s="30" t="s">
-        <v>919</v>
+      <c r="Z100" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA100" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB100" s="30" t="s">
-        <v>919</v>
+      <c r="AB100" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC100" s="56" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="101" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="49">
         <v>101</v>
       </c>
@@ -14913,20 +17029,20 @@
       <c r="Y101" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z101" s="30" t="s">
-        <v>919</v>
+      <c r="Z101" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA101" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB101" s="30" t="s">
-        <v>919</v>
+      <c r="AB101" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC101" s="56" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="102" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="49">
         <v>102</v>
       </c>
@@ -15010,20 +17126,20 @@
       <c r="Y102" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z102" s="30" t="s">
-        <v>919</v>
+      <c r="Z102" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA102" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB102" s="30" t="s">
-        <v>919</v>
+      <c r="AB102" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC102" s="56" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="103" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="49">
         <v>103</v>
       </c>
@@ -15107,20 +17223,20 @@
       <c r="Y103" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z103" s="30" t="s">
-        <v>919</v>
+      <c r="Z103" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA103" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB103" s="30" t="s">
-        <v>919</v>
+      <c r="AB103" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC103" s="56" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="104" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="49">
         <v>104</v>
       </c>
@@ -15204,20 +17320,20 @@
       <c r="Y104" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z104" s="30" t="s">
-        <v>919</v>
+      <c r="Z104" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA104" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB104" s="30" t="s">
-        <v>919</v>
+      <c r="AB104" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC104" s="56" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="105" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="49">
         <v>105</v>
       </c>
@@ -15301,20 +17417,20 @@
       <c r="Y105" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z105" s="30" t="s">
-        <v>919</v>
+      <c r="Z105" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA105" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB105" s="30" t="s">
-        <v>919</v>
+      <c r="AB105" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC105" s="56" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="106" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="49">
         <v>106</v>
       </c>
@@ -15398,20 +17514,20 @@
       <c r="Y106" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z106" s="30" t="s">
-        <v>919</v>
+      <c r="Z106" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA106" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB106" s="30" t="s">
-        <v>919</v>
+      <c r="AB106" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC106" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="107" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="49">
         <v>107</v>
       </c>
@@ -15495,20 +17611,20 @@
       <c r="Y107" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z107" s="30" t="s">
-        <v>919</v>
+      <c r="Z107" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA107" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB107" s="30" t="s">
-        <v>919</v>
+      <c r="AB107" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC107" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="108" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="49">
         <v>108</v>
       </c>
@@ -15592,20 +17708,20 @@
       <c r="Y108" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z108" s="30" t="s">
-        <v>919</v>
+      <c r="Z108" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA108" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB108" s="30" t="s">
-        <v>919</v>
+      <c r="AB108" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC108" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="109" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="49">
         <v>109</v>
       </c>
@@ -15689,20 +17805,20 @@
       <c r="Y109" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z109" s="30" t="s">
-        <v>919</v>
+      <c r="Z109" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA109" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB109" s="30" t="s">
-        <v>919</v>
+      <c r="AB109" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC109" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="110" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="49">
         <v>110</v>
       </c>
@@ -15786,20 +17902,20 @@
       <c r="Y110" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z110" s="30" t="s">
-        <v>919</v>
+      <c r="Z110" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA110" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB110" s="30" t="s">
-        <v>919</v>
+      <c r="AB110" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC110" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="111" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="49">
         <v>111</v>
       </c>
@@ -15883,20 +17999,20 @@
       <c r="Y111" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z111" s="30" t="s">
-        <v>919</v>
+      <c r="Z111" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA111" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB111" s="30" t="s">
-        <v>919</v>
+      <c r="AB111" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC111" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="112" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="49">
         <v>112</v>
       </c>
@@ -15980,20 +18096,20 @@
       <c r="Y112" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z112" s="30" t="s">
-        <v>919</v>
+      <c r="Z112" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA112" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB112" s="30" t="s">
-        <v>919</v>
+      <c r="AB112" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC112" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="113" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="49">
         <v>113</v>
       </c>
@@ -16077,20 +18193,20 @@
       <c r="Y113" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z113" s="30" t="s">
-        <v>919</v>
+      <c r="Z113" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA113" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB113" s="30" t="s">
-        <v>919</v>
+      <c r="AB113" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC113" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="114" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="49">
         <v>114</v>
       </c>
@@ -16174,20 +18290,20 @@
       <c r="Y114" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z114" s="30" t="s">
-        <v>919</v>
+      <c r="Z114" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA114" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB114" s="30" t="s">
-        <v>919</v>
+      <c r="AB114" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC114" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="115" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="49">
         <v>115</v>
       </c>
@@ -16271,20 +18387,20 @@
       <c r="Y115" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z115" s="30" t="s">
-        <v>919</v>
+      <c r="Z115" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA115" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB115" s="30" t="s">
-        <v>919</v>
+      <c r="AB115" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC115" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="116" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="49">
         <v>116</v>
       </c>
@@ -16368,20 +18484,20 @@
       <c r="Y116" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z116" s="30" t="s">
-        <v>919</v>
+      <c r="Z116" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA116" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB116" s="30" t="s">
-        <v>919</v>
+      <c r="AB116" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC116" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="117" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="49">
         <v>117</v>
       </c>
@@ -16465,20 +18581,20 @@
       <c r="Y117" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z117" s="30" t="s">
-        <v>919</v>
+      <c r="Z117" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA117" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB117" s="30" t="s">
-        <v>919</v>
+      <c r="AB117" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC117" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="118" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="49">
         <v>118</v>
       </c>
@@ -16562,20 +18678,20 @@
       <c r="Y118" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z118" s="30" t="s">
-        <v>919</v>
+      <c r="Z118" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA118" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB118" s="30" t="s">
-        <v>919</v>
+      <c r="AB118" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC118" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="119" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="49">
         <v>119</v>
       </c>
@@ -16659,20 +18775,20 @@
       <c r="Y119" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z119" s="30" t="s">
-        <v>919</v>
+      <c r="Z119" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA119" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB119" s="30" t="s">
-        <v>919</v>
+      <c r="AB119" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC119" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="120" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="49">
         <v>120</v>
       </c>
@@ -16756,20 +18872,20 @@
       <c r="Y120" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z120" s="30" t="s">
-        <v>919</v>
+      <c r="Z120" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA120" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB120" s="30" t="s">
-        <v>919</v>
+      <c r="AB120" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC120" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="121" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="49">
         <v>121</v>
       </c>
@@ -16853,20 +18969,20 @@
       <c r="Y121" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z121" s="30" t="s">
-        <v>919</v>
+      <c r="Z121" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA121" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB121" s="30" t="s">
-        <v>919</v>
+      <c r="AB121" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC121" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="122" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="49">
         <v>122</v>
       </c>
@@ -16950,20 +19066,20 @@
       <c r="Y122" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z122" s="30" t="s">
-        <v>919</v>
+      <c r="Z122" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA122" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB122" s="30" t="s">
-        <v>919</v>
+      <c r="AB122" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC122" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="123" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="49">
         <v>123</v>
       </c>
@@ -17047,20 +19163,20 @@
       <c r="Y123" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z123" s="30" t="s">
-        <v>919</v>
+      <c r="Z123" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA123" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB123" s="30" t="s">
-        <v>919</v>
+      <c r="AB123" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC123" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="124" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="49">
         <v>124</v>
       </c>
@@ -17144,20 +19260,20 @@
       <c r="Y124" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z124" s="30" t="s">
-        <v>919</v>
+      <c r="Z124" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA124" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB124" s="30" t="s">
-        <v>919</v>
+      <c r="AB124" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC124" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="125" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="49">
         <v>125</v>
       </c>
@@ -17241,20 +19357,20 @@
       <c r="Y125" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z125" s="30" t="s">
-        <v>919</v>
+      <c r="Z125" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA125" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB125" s="30" t="s">
-        <v>919</v>
+      <c r="AB125" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC125" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="126" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="49">
         <v>126</v>
       </c>
@@ -17332,26 +19448,26 @@
         <v>86</v>
       </c>
       <c r="X126" s="45" t="str">
-        <f t="shared" ref="X126:X182" si="36">CONCATENATE("Key-AMB-",A126)</f>
+        <f t="shared" ref="X126:X186" si="36">CONCATENATE("Key-AMB-",A126)</f>
         <v>Key-AMB-126</v>
       </c>
       <c r="Y126" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z126" s="30" t="s">
-        <v>919</v>
+      <c r="Z126" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA126" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB126" s="30" t="s">
-        <v>919</v>
+      <c r="AB126" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC126" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="127" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="49">
         <v>127</v>
       </c>
@@ -17435,20 +19551,20 @@
       <c r="Y127" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z127" s="30" t="s">
-        <v>919</v>
+      <c r="Z127" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA127" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB127" s="30" t="s">
-        <v>919</v>
+      <c r="AB127" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC127" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="128" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="49">
         <v>128</v>
       </c>
@@ -17532,20 +19648,20 @@
       <c r="Y128" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z128" s="30" t="s">
-        <v>919</v>
+      <c r="Z128" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA128" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB128" s="30" t="s">
-        <v>919</v>
+      <c r="AB128" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC128" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="129" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="49">
         <v>129</v>
       </c>
@@ -17629,20 +19745,20 @@
       <c r="Y129" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z129" s="30" t="s">
-        <v>919</v>
+      <c r="Z129" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA129" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB129" s="30" t="s">
-        <v>919</v>
+      <c r="AB129" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC129" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="130" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="49">
         <v>130</v>
       </c>
@@ -17726,20 +19842,20 @@
       <c r="Y130" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z130" s="30" t="s">
-        <v>919</v>
+      <c r="Z130" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA130" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB130" s="30" t="s">
-        <v>919</v>
+      <c r="AB130" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC130" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="131" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="49">
         <v>131</v>
       </c>
@@ -17823,20 +19939,20 @@
       <c r="Y131" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z131" s="30" t="s">
-        <v>919</v>
+      <c r="Z131" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA131" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB131" s="30" t="s">
-        <v>919</v>
+      <c r="AB131" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC131" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="132" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="49">
         <v>132</v>
       </c>
@@ -17920,20 +20036,20 @@
       <c r="Y132" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z132" s="30" t="s">
-        <v>919</v>
+      <c r="Z132" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA132" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB132" s="30" t="s">
-        <v>919</v>
+      <c r="AB132" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC132" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="133" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="49">
         <v>133</v>
       </c>
@@ -18017,20 +20133,20 @@
       <c r="Y133" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z133" s="30" t="s">
-        <v>919</v>
+      <c r="Z133" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA133" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB133" s="30" t="s">
-        <v>919</v>
+      <c r="AB133" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC133" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="134" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="49">
         <v>134</v>
       </c>
@@ -18114,20 +20230,20 @@
       <c r="Y134" s="30" t="s">
         <v>556</v>
       </c>
-      <c r="Z134" s="30" t="s">
-        <v>919</v>
+      <c r="Z134" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA134" s="41" t="s">
         <v>204</v>
       </c>
-      <c r="AB134" s="30" t="s">
-        <v>919</v>
+      <c r="AB134" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC134" s="56" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="135" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="49">
         <v>135</v>
       </c>
@@ -18211,20 +20327,20 @@
       <c r="Y135" s="30" t="s">
         <v>556</v>
       </c>
-      <c r="Z135" s="30" t="s">
-        <v>919</v>
+      <c r="Z135" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA135" s="41" t="s">
         <v>204</v>
       </c>
-      <c r="AB135" s="30" t="s">
-        <v>919</v>
+      <c r="AB135" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC135" s="56" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="136" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="49">
         <v>136</v>
       </c>
@@ -18308,20 +20424,20 @@
       <c r="Y136" s="30" t="s">
         <v>556</v>
       </c>
-      <c r="Z136" s="30" t="s">
-        <v>919</v>
+      <c r="Z136" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA136" s="41" t="s">
         <v>204</v>
       </c>
-      <c r="AB136" s="30" t="s">
-        <v>919</v>
+      <c r="AB136" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC136" s="56" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="137" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="49">
         <v>137</v>
       </c>
@@ -18405,20 +20521,20 @@
       <c r="Y137" s="30" t="s">
         <v>556</v>
       </c>
-      <c r="Z137" s="30" t="s">
-        <v>919</v>
+      <c r="Z137" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA137" s="41" t="s">
         <v>204</v>
       </c>
-      <c r="AB137" s="30" t="s">
-        <v>919</v>
+      <c r="AB137" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC137" s="56" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="138" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="49">
         <v>138</v>
       </c>
@@ -18502,20 +20618,20 @@
       <c r="Y138" s="30" t="s">
         <v>556</v>
       </c>
-      <c r="Z138" s="30" t="s">
-        <v>919</v>
+      <c r="Z138" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA138" s="41" t="s">
         <v>204</v>
       </c>
-      <c r="AB138" s="30" t="s">
-        <v>919</v>
+      <c r="AB138" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC138" s="56" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="139" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="49">
         <v>139</v>
       </c>
@@ -18599,20 +20715,20 @@
       <c r="Y139" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z139" s="30" t="s">
-        <v>919</v>
+      <c r="Z139" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA139" s="41" t="s">
         <v>204</v>
       </c>
-      <c r="AB139" s="30" t="s">
-        <v>919</v>
+      <c r="AB139" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC139" s="56" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="140" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="49">
         <v>140</v>
       </c>
@@ -18696,20 +20812,20 @@
       <c r="Y140" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z140" s="30" t="s">
-        <v>919</v>
+      <c r="Z140" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA140" s="41" t="s">
         <v>204</v>
       </c>
-      <c r="AB140" s="30" t="s">
-        <v>919</v>
+      <c r="AB140" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC140" s="56" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="141" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="49">
         <v>141</v>
       </c>
@@ -18793,20 +20909,20 @@
       <c r="Y141" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z141" s="30" t="s">
-        <v>919</v>
+      <c r="Z141" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA141" s="41" t="s">
         <v>204</v>
       </c>
-      <c r="AB141" s="30" t="s">
-        <v>919</v>
+      <c r="AB141" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC141" s="56" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="142" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="49">
         <v>142</v>
       </c>
@@ -18890,20 +21006,20 @@
       <c r="Y142" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z142" s="30" t="s">
-        <v>919</v>
+      <c r="Z142" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA142" s="41" t="s">
         <v>204</v>
       </c>
-      <c r="AB142" s="30" t="s">
-        <v>919</v>
+      <c r="AB142" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC142" s="56" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="143" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="49">
         <v>143</v>
       </c>
@@ -18987,20 +21103,20 @@
       <c r="Y143" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z143" s="30" t="s">
-        <v>919</v>
+      <c r="Z143" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA143" s="41" t="s">
         <v>204</v>
       </c>
-      <c r="AB143" s="30" t="s">
-        <v>919</v>
+      <c r="AB143" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC143" s="56" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="144" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="49">
         <v>144</v>
       </c>
@@ -19084,20 +21200,20 @@
       <c r="Y144" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z144" s="30" t="s">
-        <v>919</v>
+      <c r="Z144" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA144" s="41" t="s">
         <v>204</v>
       </c>
-      <c r="AB144" s="30" t="s">
-        <v>919</v>
+      <c r="AB144" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC144" s="56" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="145" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="49">
         <v>145</v>
       </c>
@@ -19181,20 +21297,20 @@
       <c r="Y145" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z145" s="30" t="s">
-        <v>919</v>
+      <c r="Z145" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA145" s="41" t="s">
         <v>204</v>
       </c>
-      <c r="AB145" s="30" t="s">
-        <v>919</v>
+      <c r="AB145" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC145" s="56" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="146" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="49">
         <v>146</v>
       </c>
@@ -19278,20 +21394,20 @@
       <c r="Y146" s="30" t="s">
         <v>557</v>
       </c>
-      <c r="Z146" s="30" t="s">
-        <v>919</v>
+      <c r="Z146" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA146" s="41" t="s">
         <v>205</v>
       </c>
-      <c r="AB146" s="30" t="s">
-        <v>919</v>
+      <c r="AB146" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC146" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="147" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="49">
         <v>147</v>
       </c>
@@ -19375,20 +21491,20 @@
       <c r="Y147" s="30" t="s">
         <v>557</v>
       </c>
-      <c r="Z147" s="30" t="s">
-        <v>919</v>
+      <c r="Z147" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA147" s="41" t="s">
         <v>206</v>
       </c>
-      <c r="AB147" s="30" t="s">
-        <v>919</v>
+      <c r="AB147" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC147" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="148" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="49">
         <v>148</v>
       </c>
@@ -19472,20 +21588,20 @@
       <c r="Y148" s="30" t="s">
         <v>557</v>
       </c>
-      <c r="Z148" s="30" t="s">
-        <v>919</v>
+      <c r="Z148" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA148" s="41" t="s">
         <v>207</v>
       </c>
-      <c r="AB148" s="30" t="s">
-        <v>919</v>
+      <c r="AB148" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC148" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="149" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="49">
         <v>149</v>
       </c>
@@ -19569,20 +21685,20 @@
       <c r="Y149" s="30" t="s">
         <v>557</v>
       </c>
-      <c r="Z149" s="30" t="s">
-        <v>919</v>
+      <c r="Z149" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA149" s="41" t="s">
         <v>208</v>
       </c>
-      <c r="AB149" s="30" t="s">
-        <v>919</v>
+      <c r="AB149" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC149" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="150" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="49">
         <v>150</v>
       </c>
@@ -19666,20 +21782,20 @@
       <c r="Y150" s="30" t="s">
         <v>557</v>
       </c>
-      <c r="Z150" s="30" t="s">
-        <v>919</v>
+      <c r="Z150" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA150" s="41" t="s">
         <v>209</v>
       </c>
-      <c r="AB150" s="30" t="s">
-        <v>919</v>
+      <c r="AB150" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC150" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="151" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="49">
         <v>151</v>
       </c>
@@ -19763,20 +21879,20 @@
       <c r="Y151" s="30" t="s">
         <v>557</v>
       </c>
-      <c r="Z151" s="30" t="s">
-        <v>919</v>
+      <c r="Z151" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA151" s="41" t="s">
         <v>210</v>
       </c>
-      <c r="AB151" s="30" t="s">
-        <v>919</v>
+      <c r="AB151" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC151" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="152" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="49">
         <v>152</v>
       </c>
@@ -19860,20 +21976,20 @@
       <c r="Y152" s="30" t="s">
         <v>557</v>
       </c>
-      <c r="Z152" s="30" t="s">
-        <v>919</v>
+      <c r="Z152" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA152" s="41" t="s">
         <v>211</v>
       </c>
-      <c r="AB152" s="30" t="s">
-        <v>919</v>
+      <c r="AB152" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC152" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="153" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="49">
         <v>153</v>
       </c>
@@ -19957,20 +22073,20 @@
       <c r="Y153" s="30" t="s">
         <v>557</v>
       </c>
-      <c r="Z153" s="30" t="s">
-        <v>919</v>
+      <c r="Z153" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA153" s="41" t="s">
         <v>212</v>
       </c>
-      <c r="AB153" s="30" t="s">
-        <v>919</v>
+      <c r="AB153" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC153" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="154" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="49">
         <v>154</v>
       </c>
@@ -20054,20 +22170,20 @@
       <c r="Y154" s="30" t="s">
         <v>557</v>
       </c>
-      <c r="Z154" s="30" t="s">
-        <v>919</v>
+      <c r="Z154" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA154" s="41" t="s">
         <v>213</v>
       </c>
-      <c r="AB154" s="30" t="s">
-        <v>919</v>
+      <c r="AB154" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC154" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="155" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="49">
         <v>155</v>
       </c>
@@ -20151,20 +22267,20 @@
       <c r="Y155" s="30" t="s">
         <v>557</v>
       </c>
-      <c r="Z155" s="30" t="s">
-        <v>919</v>
+      <c r="Z155" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA155" s="41" t="s">
         <v>215</v>
       </c>
-      <c r="AB155" s="30" t="s">
-        <v>919</v>
+      <c r="AB155" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC155" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="156" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="49">
         <v>156</v>
       </c>
@@ -20248,20 +22364,20 @@
       <c r="Y156" s="30" t="s">
         <v>557</v>
       </c>
-      <c r="Z156" s="30" t="s">
-        <v>919</v>
+      <c r="Z156" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA156" s="41" t="s">
         <v>214</v>
       </c>
-      <c r="AB156" s="30" t="s">
-        <v>919</v>
+      <c r="AB156" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC156" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="157" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="49">
         <v>157</v>
       </c>
@@ -20345,20 +22461,20 @@
       <c r="Y157" s="30" t="s">
         <v>557</v>
       </c>
-      <c r="Z157" s="30" t="s">
-        <v>919</v>
+      <c r="Z157" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA157" s="41" t="s">
         <v>213</v>
       </c>
-      <c r="AB157" s="30" t="s">
-        <v>919</v>
+      <c r="AB157" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC157" s="56" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="158" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="49">
         <v>158</v>
       </c>
@@ -20442,20 +22558,20 @@
       <c r="Y158" s="48" t="s">
         <v>228</v>
       </c>
-      <c r="Z158" s="30" t="s">
-        <v>919</v>
+      <c r="Z158" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA158" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="AB158" s="30" t="s">
-        <v>919</v>
+      <c r="AB158" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC158" s="56" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="159" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="49">
         <v>159</v>
       </c>
@@ -20539,20 +22655,20 @@
       <c r="Y159" s="48" t="s">
         <v>234</v>
       </c>
-      <c r="Z159" s="30" t="s">
-        <v>919</v>
+      <c r="Z159" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA159" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="AB159" s="30" t="s">
-        <v>919</v>
+      <c r="AB159" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC159" s="56" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="160" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="49">
         <v>160</v>
       </c>
@@ -20636,20 +22752,20 @@
       <c r="Y160" s="48" t="s">
         <v>229</v>
       </c>
-      <c r="Z160" s="30" t="s">
-        <v>919</v>
+      <c r="Z160" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA160" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="AB160" s="30" t="s">
-        <v>919</v>
+      <c r="AB160" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC160" s="56" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="161" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="49">
         <v>161</v>
       </c>
@@ -20733,20 +22849,20 @@
       <c r="Y161" s="48" t="s">
         <v>233</v>
       </c>
-      <c r="Z161" s="30" t="s">
-        <v>919</v>
+      <c r="Z161" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA161" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="AB161" s="30" t="s">
-        <v>919</v>
+      <c r="AB161" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC161" s="56" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="162" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="49">
         <v>162</v>
       </c>
@@ -20830,20 +22946,20 @@
       <c r="Y162" s="48" t="s">
         <v>230</v>
       </c>
-      <c r="Z162" s="30" t="s">
-        <v>919</v>
+      <c r="Z162" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA162" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="AB162" s="30" t="s">
-        <v>919</v>
+      <c r="AB162" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC162" s="56" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="163" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="49">
         <v>163</v>
       </c>
@@ -20927,20 +23043,20 @@
       <c r="Y163" s="48" t="s">
         <v>232</v>
       </c>
-      <c r="Z163" s="30" t="s">
-        <v>919</v>
+      <c r="Z163" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA163" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="AB163" s="30" t="s">
-        <v>919</v>
+      <c r="AB163" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC163" s="56" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="164" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="49">
         <v>164</v>
       </c>
@@ -21024,20 +23140,20 @@
       <c r="Y164" s="48" t="s">
         <v>231</v>
       </c>
-      <c r="Z164" s="30" t="s">
-        <v>919</v>
+      <c r="Z164" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA164" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="AB164" s="30" t="s">
-        <v>919</v>
+      <c r="AB164" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC164" s="56" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="165" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="49">
         <v>165</v>
       </c>
@@ -21121,20 +23237,20 @@
       <c r="Y165" s="30" t="s">
         <v>242</v>
       </c>
-      <c r="Z165" s="30" t="s">
-        <v>919</v>
+      <c r="Z165" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA165" s="30" t="s">
         <v>243</v>
       </c>
-      <c r="AB165" s="30" t="s">
-        <v>919</v>
+      <c r="AB165" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC165" s="56" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="166" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="49">
         <v>166</v>
       </c>
@@ -21218,20 +23334,20 @@
       <c r="Y166" s="30" t="s">
         <v>242</v>
       </c>
-      <c r="Z166" s="30" t="s">
-        <v>919</v>
+      <c r="Z166" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA166" s="30" t="s">
         <v>243</v>
       </c>
-      <c r="AB166" s="30" t="s">
-        <v>919</v>
+      <c r="AB166" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC166" s="56" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="167" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="49">
         <v>167</v>
       </c>
@@ -21315,20 +23431,20 @@
       <c r="Y167" s="30" t="s">
         <v>242</v>
       </c>
-      <c r="Z167" s="30" t="s">
-        <v>919</v>
+      <c r="Z167" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA167" s="30" t="s">
         <v>243</v>
       </c>
-      <c r="AB167" s="30" t="s">
-        <v>919</v>
+      <c r="AB167" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC167" s="56" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="168" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="49">
         <v>168</v>
       </c>
@@ -21412,20 +23528,20 @@
       <c r="Y168" s="30" t="s">
         <v>242</v>
       </c>
-      <c r="Z168" s="30" t="s">
-        <v>919</v>
+      <c r="Z168" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA168" s="30" t="s">
         <v>243</v>
       </c>
-      <c r="AB168" s="30" t="s">
-        <v>919</v>
+      <c r="AB168" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC168" s="56" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="169" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="49">
         <v>169</v>
       </c>
@@ -21509,20 +23625,20 @@
       <c r="Y169" s="30" t="s">
         <v>242</v>
       </c>
-      <c r="Z169" s="30" t="s">
-        <v>919</v>
+      <c r="Z169" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA169" s="30" t="s">
         <v>243</v>
       </c>
-      <c r="AB169" s="30" t="s">
-        <v>919</v>
+      <c r="AB169" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC169" s="56" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="170" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="49">
         <v>170</v>
       </c>
@@ -21603,23 +23719,23 @@
         <f t="shared" ref="X170:X171" si="48">CONCATENATE("Key-AMB-",A170)</f>
         <v>Key-AMB-170</v>
       </c>
-      <c r="Y170" s="56" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z170" s="30" t="s">
-        <v>919</v>
+      <c r="Y170" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z170" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA170" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="AB170" s="30" t="s">
-        <v>919</v>
+      <c r="AB170" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC170" s="56" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="171" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="49">
         <v>171</v>
       </c>
@@ -21700,23 +23816,23 @@
         <f t="shared" si="48"/>
         <v>Key-AMB-171</v>
       </c>
-      <c r="Y171" s="56" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z171" s="30" t="s">
-        <v>919</v>
+      <c r="Y171" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z171" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA171" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="AB171" s="30" t="s">
-        <v>919</v>
+      <c r="AB171" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC171" s="56" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="172" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="49">
         <v>172</v>
       </c>
@@ -21797,23 +23913,23 @@
         <f t="shared" si="36"/>
         <v>Key-AMB-172</v>
       </c>
-      <c r="Y172" s="56" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z172" s="30" t="s">
-        <v>919</v>
+      <c r="Y172" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z172" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA172" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="AB172" s="30" t="s">
-        <v>919</v>
+      <c r="AB172" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC172" s="56" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="173" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="49">
         <v>173</v>
       </c>
@@ -21897,20 +24013,20 @@
       <c r="Y173" s="30" t="s">
         <v>484</v>
       </c>
-      <c r="Z173" s="30" t="s">
-        <v>919</v>
+      <c r="Z173" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA173" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB173" s="30" t="s">
-        <v>919</v>
+      <c r="AB173" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC173" s="56" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="174" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="49">
         <v>174</v>
       </c>
@@ -21994,20 +24110,20 @@
       <c r="Y174" s="30" t="s">
         <v>553</v>
       </c>
-      <c r="Z174" s="30" t="s">
-        <v>919</v>
+      <c r="Z174" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA174" s="41" t="s">
         <v>191</v>
       </c>
-      <c r="AB174" s="30" t="s">
-        <v>919</v>
+      <c r="AB174" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC174" s="56" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="175" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="49">
         <v>175</v>
       </c>
@@ -22091,20 +24207,20 @@
       <c r="Y175" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z175" s="30" t="s">
-        <v>919</v>
+      <c r="Z175" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA175" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB175" s="30" t="s">
-        <v>919</v>
+      <c r="AB175" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC175" s="56" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="176" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="49">
         <v>176</v>
       </c>
@@ -22185,23 +24301,23 @@
         <f t="shared" si="36"/>
         <v>Key-AMB-176</v>
       </c>
-      <c r="Y176" s="56" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z176" s="30" t="s">
-        <v>919</v>
+      <c r="Y176" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z176" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA176" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="AB176" s="30" t="s">
-        <v>919</v>
+      <c r="AB176" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC176" s="56" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="177" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="49">
         <v>177</v>
       </c>
@@ -22279,26 +24395,26 @@
         <v>86</v>
       </c>
       <c r="X177" s="45" t="str">
-        <f t="shared" ref="X177" si="75">CONCATENATE("Key-AMB-",A177)</f>
+        <f t="shared" si="36"/>
         <v>Key-AMB-177</v>
       </c>
-      <c r="Y177" s="56" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z177" s="30" t="s">
-        <v>919</v>
+      <c r="Y177" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z177" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA177" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="AB177" s="30" t="s">
-        <v>919</v>
+      <c r="AB177" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC177" s="56" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="178" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="49">
         <v>178</v>
       </c>
@@ -22379,23 +24495,23 @@
         <f t="shared" si="36"/>
         <v>Key-AMB-178</v>
       </c>
-      <c r="Y178" s="56" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z178" s="30" t="s">
-        <v>919</v>
+      <c r="Y178" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z178" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA178" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="AB178" s="30" t="s">
-        <v>919</v>
+      <c r="AB178" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC178" s="56" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="179" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="49">
         <v>179</v>
       </c>
@@ -22430,11 +24546,11 @@
         <v>10</v>
       </c>
       <c r="L179" s="29" t="str">
-        <f t="shared" ref="L179:M181" si="76">CONCATENATE("", C179)</f>
+        <f t="shared" ref="L179:M181" si="75">CONCATENATE("", C179)</f>
         <v>De.Arquitetura</v>
       </c>
       <c r="M179" s="29" t="str">
-        <f t="shared" si="76"/>
+        <f t="shared" si="75"/>
         <v>Layout</v>
       </c>
       <c r="N179" s="29" t="str">
@@ -22479,20 +24595,20 @@
       <c r="Y179" s="30" t="s">
         <v>484</v>
       </c>
-      <c r="Z179" s="30" t="s">
-        <v>919</v>
+      <c r="Z179" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA179" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB179" s="30" t="s">
-        <v>919</v>
+      <c r="AB179" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC179" s="56" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="180" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="49">
         <v>180</v>
       </c>
@@ -22527,15 +24643,15 @@
         <v>10</v>
       </c>
       <c r="L180" s="29" t="str">
-        <f t="shared" si="76"/>
+        <f t="shared" si="75"/>
         <v>De.Arquitetura</v>
       </c>
       <c r="M180" s="29" t="str">
-        <f t="shared" si="76"/>
+        <f t="shared" si="75"/>
         <v>Layout</v>
       </c>
       <c r="N180" s="29" t="str">
-        <f t="shared" ref="N180:O181" si="77">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E180),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N180:O181" si="76">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E180),"."," ")," De "," de "))</f>
         <v>Espaços Novos</v>
       </c>
       <c r="O180" s="29" t="str">
@@ -22576,20 +24692,20 @@
       <c r="Y180" s="30" t="s">
         <v>553</v>
       </c>
-      <c r="Z180" s="30" t="s">
-        <v>919</v>
+      <c r="Z180" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA180" s="41" t="s">
         <v>191</v>
       </c>
-      <c r="AB180" s="30" t="s">
-        <v>919</v>
+      <c r="AB180" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC180" s="56" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="181" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="49">
         <v>181</v>
       </c>
@@ -22624,19 +24740,19 @@
         <v>10</v>
       </c>
       <c r="L181" s="29" t="str">
+        <f t="shared" si="75"/>
+        <v>De.Arquitetura</v>
+      </c>
+      <c r="M181" s="29" t="str">
+        <f t="shared" si="75"/>
+        <v>Layout</v>
+      </c>
+      <c r="N181" s="29" t="str">
         <f t="shared" si="76"/>
-        <v>De.Arquitetura</v>
-      </c>
-      <c r="M181" s="29" t="str">
+        <v>Espaços Novos</v>
+      </c>
+      <c r="O181" s="29" t="str">
         <f t="shared" si="76"/>
-        <v>Layout</v>
-      </c>
-      <c r="N181" s="29" t="str">
-        <f t="shared" si="77"/>
-        <v>Espaços Novos</v>
-      </c>
-      <c r="O181" s="29" t="str">
-        <f t="shared" si="77"/>
         <v>Compartimento Novo</v>
       </c>
       <c r="P181" s="30" t="s">
@@ -22652,15 +24768,15 @@
         <v>10</v>
       </c>
       <c r="T181" s="56" t="str">
-        <f t="shared" ref="T181:V182" si="78">SUBSTITUTE(C181, ".", " ")</f>
+        <f t="shared" ref="T181:V186" si="77">SUBSTITUTE(C181, ".", " ")</f>
         <v>De Arquitetura</v>
       </c>
       <c r="U181" s="56" t="str">
-        <f t="shared" si="78"/>
+        <f t="shared" si="77"/>
         <v>Layout</v>
       </c>
       <c r="V181" s="56" t="str">
-        <f t="shared" si="78"/>
+        <f t="shared" si="77"/>
         <v>Espaços Novos</v>
       </c>
       <c r="W181" s="30" t="s">
@@ -22673,20 +24789,20 @@
       <c r="Y181" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="Z181" s="30" t="s">
-        <v>919</v>
+      <c r="Z181" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AA181" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="AB181" s="30" t="s">
-        <v>919</v>
+      <c r="AB181" s="63" t="s">
+        <v>10</v>
       </c>
       <c r="AC181" s="56" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="182" spans="1:29" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:29" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="49">
         <v>182</v>
       </c>
@@ -22694,17 +24810,17 @@
         <v>79</v>
       </c>
       <c r="C182" s="65" t="s">
+        <v>922</v>
+      </c>
+      <c r="D182" s="65" t="s">
+        <v>924</v>
+      </c>
+      <c r="E182" s="65" t="s">
         <v>923</v>
       </c>
-      <c r="D182" s="65" t="s">
+      <c r="F182" s="65" t="s">
         <v>925</v>
       </c>
-      <c r="E182" s="65" t="s">
-        <v>924</v>
-      </c>
-      <c r="F182" s="65" t="s">
-        <v>926</v>
-      </c>
       <c r="G182" s="44" t="s">
         <v>10</v>
       </c>
@@ -22721,43 +24837,43 @@
         <v>10</v>
       </c>
       <c r="L182" s="29" t="str">
-        <f t="shared" ref="L182:O182" si="79">SUBSTITUTE(CONCATENATE("", C182), ".", " ")</f>
+        <f t="shared" ref="L182:O186" si="78">SUBSTITUTE(CONCATENATE("", C182), ".", " ")</f>
         <v>De API</v>
       </c>
       <c r="M182" s="29" t="str">
-        <f t="shared" si="79"/>
-        <v>Macros</v>
-      </c>
-      <c r="N182" s="29" t="str">
-        <f t="shared" si="79"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O182" s="29" t="str">
-        <f t="shared" si="79"/>
-        <v>API Revit</v>
-      </c>
-      <c r="P182" s="30" t="s">
-        <v>927</v>
-      </c>
-      <c r="Q182" s="30" t="s">
-        <v>928</v>
-      </c>
-      <c r="R182" s="30" t="s">
-        <v>929</v>
-      </c>
-      <c r="S182" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="T182" s="30" t="str">
-        <f t="shared" si="78"/>
-        <v>De API</v>
-      </c>
-      <c r="U182" s="30" t="str">
         <f t="shared" si="78"/>
         <v>Macros</v>
       </c>
+      <c r="N182" s="29" t="str">
+        <f t="shared" si="78"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O182" s="29" t="str">
+        <f t="shared" si="78"/>
+        <v>Função Auxiliar</v>
+      </c>
+      <c r="P182" s="30" t="s">
+        <v>926</v>
+      </c>
+      <c r="Q182" s="30" t="s">
+        <v>927</v>
+      </c>
+      <c r="R182" s="30" t="s">
+        <v>928</v>
+      </c>
+      <c r="S182" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="T182" s="30" t="str">
+        <f t="shared" si="77"/>
+        <v>De API</v>
+      </c>
+      <c r="U182" s="30" t="str">
+        <f t="shared" si="77"/>
+        <v>Macros</v>
+      </c>
       <c r="V182" s="56" t="str">
-        <f t="shared" si="78"/>
+        <f t="shared" si="77"/>
         <v>Métodos</v>
       </c>
       <c r="W182" s="30" t="s">
@@ -22783,243 +24899,619 @@
         <v>10</v>
       </c>
     </row>
+    <row r="183" spans="1:29" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A183" s="49">
+        <v>183</v>
+      </c>
+      <c r="B183" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="C183" s="65" t="s">
+        <v>922</v>
+      </c>
+      <c r="D183" s="65" t="s">
+        <v>924</v>
+      </c>
+      <c r="E183" s="65" t="s">
+        <v>923</v>
+      </c>
+      <c r="F183" s="65" t="s">
+        <v>929</v>
+      </c>
+      <c r="G183" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="H183" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="I183" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="J183" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="K183" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="L183" s="29" t="str">
+        <f t="shared" si="78"/>
+        <v>De API</v>
+      </c>
+      <c r="M183" s="29" t="str">
+        <f t="shared" si="78"/>
+        <v>Macros</v>
+      </c>
+      <c r="N183" s="29" t="str">
+        <f t="shared" si="78"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O183" s="29" t="str">
+        <f t="shared" si="78"/>
+        <v>Função Global</v>
+      </c>
+      <c r="P183" s="30" t="s">
+        <v>930</v>
+      </c>
+      <c r="Q183" s="30" t="s">
+        <v>931</v>
+      </c>
+      <c r="R183" s="30" t="s">
+        <v>932</v>
+      </c>
+      <c r="S183" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="T183" s="30" t="str">
+        <f t="shared" si="77"/>
+        <v>De API</v>
+      </c>
+      <c r="U183" s="30" t="str">
+        <f t="shared" si="77"/>
+        <v>Macros</v>
+      </c>
+      <c r="V183" s="56" t="str">
+        <f t="shared" si="77"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W183" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="X183" s="45" t="str">
+        <f t="shared" si="36"/>
+        <v>Key-AMB-183</v>
+      </c>
+      <c r="Y183" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z183" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA183" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB183" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC183" s="63" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="184" spans="1:29" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A184" s="49">
+        <v>184</v>
+      </c>
+      <c r="B184" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="C184" s="65" t="s">
+        <v>922</v>
+      </c>
+      <c r="D184" s="65" t="s">
+        <v>924</v>
+      </c>
+      <c r="E184" s="65" t="s">
+        <v>923</v>
+      </c>
+      <c r="F184" s="65" t="s">
+        <v>933</v>
+      </c>
+      <c r="G184" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="H184" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="I184" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="J184" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="K184" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="L184" s="29" t="str">
+        <f t="shared" si="78"/>
+        <v>De API</v>
+      </c>
+      <c r="M184" s="29" t="str">
+        <f t="shared" si="78"/>
+        <v>Macros</v>
+      </c>
+      <c r="N184" s="29" t="str">
+        <f t="shared" si="78"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O184" s="29" t="str">
+        <f t="shared" si="78"/>
+        <v>Função Local</v>
+      </c>
+      <c r="P184" s="30" t="s">
+        <v>934</v>
+      </c>
+      <c r="Q184" s="30" t="s">
+        <v>935</v>
+      </c>
+      <c r="R184" s="30" t="s">
+        <v>936</v>
+      </c>
+      <c r="S184" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="T184" s="30" t="str">
+        <f t="shared" si="77"/>
+        <v>De API</v>
+      </c>
+      <c r="U184" s="30" t="str">
+        <f t="shared" si="77"/>
+        <v>Macros</v>
+      </c>
+      <c r="V184" s="56" t="str">
+        <f t="shared" si="77"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W184" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="X184" s="45" t="str">
+        <f t="shared" si="36"/>
+        <v>Key-AMB-184</v>
+      </c>
+      <c r="Y184" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z184" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA184" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB184" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC184" s="63" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="185" spans="1:29" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A185" s="49">
+        <v>185</v>
+      </c>
+      <c r="B185" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="C185" s="65" t="s">
+        <v>922</v>
+      </c>
+      <c r="D185" s="65" t="s">
+        <v>924</v>
+      </c>
+      <c r="E185" s="65" t="s">
+        <v>923</v>
+      </c>
+      <c r="F185" s="65" t="s">
+        <v>937</v>
+      </c>
+      <c r="G185" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="H185" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="I185" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="J185" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="K185" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="L185" s="29" t="str">
+        <f t="shared" si="78"/>
+        <v>De API</v>
+      </c>
+      <c r="M185" s="29" t="str">
+        <f t="shared" si="78"/>
+        <v>Macros</v>
+      </c>
+      <c r="N185" s="29" t="str">
+        <f t="shared" si="78"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O185" s="29" t="str">
+        <f t="shared" si="78"/>
+        <v>Função Filtro</v>
+      </c>
+      <c r="P185" s="30" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q185" s="30" t="s">
+        <v>939</v>
+      </c>
+      <c r="R185" s="30" t="s">
+        <v>940</v>
+      </c>
+      <c r="S185" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="T185" s="30" t="str">
+        <f t="shared" si="77"/>
+        <v>De API</v>
+      </c>
+      <c r="U185" s="30" t="str">
+        <f t="shared" si="77"/>
+        <v>Macros</v>
+      </c>
+      <c r="V185" s="56" t="str">
+        <f t="shared" si="77"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W185" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="X185" s="45" t="str">
+        <f t="shared" si="36"/>
+        <v>Key-AMB-185</v>
+      </c>
+      <c r="Y185" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z185" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA185" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB185" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC185" s="63" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="186" spans="1:29" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A186" s="49">
+        <v>186</v>
+      </c>
+      <c r="B186" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="C186" s="65" t="s">
+        <v>922</v>
+      </c>
+      <c r="D186" s="65" t="s">
+        <v>924</v>
+      </c>
+      <c r="E186" s="65" t="s">
+        <v>941</v>
+      </c>
+      <c r="F186" s="65" t="s">
+        <v>942</v>
+      </c>
+      <c r="G186" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="H186" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="I186" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="J186" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="K186" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="L186" s="29" t="str">
+        <f t="shared" si="78"/>
+        <v>De API</v>
+      </c>
+      <c r="M186" s="29" t="str">
+        <f t="shared" si="78"/>
+        <v>Macros</v>
+      </c>
+      <c r="N186" s="29" t="str">
+        <f t="shared" si="78"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="O186" s="29" t="str">
+        <f t="shared" si="78"/>
+        <v>Bloco de Código</v>
+      </c>
+      <c r="P186" s="30" t="s">
+        <v>943</v>
+      </c>
+      <c r="Q186" s="30" t="s">
+        <v>944</v>
+      </c>
+      <c r="R186" s="30" t="s">
+        <v>945</v>
+      </c>
+      <c r="S186" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="T186" s="30" t="str">
+        <f t="shared" si="77"/>
+        <v>De API</v>
+      </c>
+      <c r="U186" s="30" t="str">
+        <f t="shared" si="77"/>
+        <v>Macros</v>
+      </c>
+      <c r="V186" s="56" t="str">
+        <f t="shared" si="77"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="W186" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="X186" s="45" t="str">
+        <f t="shared" si="36"/>
+        <v>Key-AMB-186</v>
+      </c>
+      <c r="Y186" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z186" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA186" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB186" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC186" s="63" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="B182">
-    <cfRule type="cellIs" dxfId="105" priority="2" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B170:D181">
-    <cfRule type="cellIs" dxfId="104" priority="60" operator="equal">
+    <cfRule type="cellIs" dxfId="321" priority="63" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:F9 L2:P9">
-    <cfRule type="cellIs" dxfId="103" priority="52" operator="equal">
+    <cfRule type="cellIs" dxfId="320" priority="55" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D50:F73">
-    <cfRule type="cellIs" dxfId="102" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="319" priority="40" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D81:F86">
-    <cfRule type="cellIs" dxfId="101" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="318" priority="32" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D87:F100">
-    <cfRule type="cellIs" dxfId="100" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="317" priority="24" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E22:F28 D29:F48 D74:F80 E101:F117 D134:F157 A2:A182 D101:D133 K157:P157">
-    <cfRule type="cellIs" dxfId="99" priority="154" operator="equal">
+  <conditionalFormatting sqref="E22:F28 D29:F48 D74:F80 E101:F117 D134:F157 D101:D133 K157:P157 A2:A186">
+    <cfRule type="cellIs" dxfId="0" priority="157" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E165:F169 L158:O164 L165:P169">
-    <cfRule type="cellIs" dxfId="98" priority="133" operator="equal">
+    <cfRule type="cellIs" dxfId="316" priority="136" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E171:F172">
-    <cfRule type="cellIs" dxfId="97" priority="70" operator="equal">
+    <cfRule type="cellIs" dxfId="315" priority="73" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F9">
-    <cfRule type="duplicateValues" dxfId="96" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="95" priority="57"/>
-    <cfRule type="duplicateValues" dxfId="94" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="93" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="92" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="314" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="313" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="312" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="311" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="310" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F10:F21">
-    <cfRule type="duplicateValues" dxfId="91" priority="152"/>
-    <cfRule type="duplicateValues" dxfId="90" priority="149"/>
-    <cfRule type="duplicateValues" dxfId="89" priority="150"/>
-    <cfRule type="duplicateValues" dxfId="88" priority="151"/>
-    <cfRule type="duplicateValues" dxfId="87" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="309" priority="152"/>
+    <cfRule type="duplicateValues" dxfId="308" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="307" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="306" priority="156"/>
+    <cfRule type="duplicateValues" dxfId="305" priority="154"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F49:F67">
-    <cfRule type="duplicateValues" dxfId="86" priority="297"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="295"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="299"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="298"/>
-    <cfRule type="duplicateValues" dxfId="82" priority="300"/>
+    <cfRule type="duplicateValues" dxfId="304" priority="300"/>
+    <cfRule type="duplicateValues" dxfId="303" priority="298"/>
+    <cfRule type="duplicateValues" dxfId="302" priority="301"/>
+    <cfRule type="duplicateValues" dxfId="301" priority="302"/>
+    <cfRule type="duplicateValues" dxfId="300" priority="303"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F68:F73">
-    <cfRule type="duplicateValues" dxfId="81" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="299" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="298" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="297" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="296" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="295" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="294" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="293" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F74:F80 F22:F48 F101:F117">
-    <cfRule type="duplicateValues" dxfId="74" priority="270"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="268"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="267"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="269"/>
+    <cfRule type="duplicateValues" dxfId="292" priority="270"/>
+    <cfRule type="duplicateValues" dxfId="291" priority="271"/>
+    <cfRule type="duplicateValues" dxfId="290" priority="272"/>
+    <cfRule type="duplicateValues" dxfId="289" priority="273"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F81:F86">
-    <cfRule type="duplicateValues" dxfId="70" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="288" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="287" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="286" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="285" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="284" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="283" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="282" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F87:F100">
-    <cfRule type="duplicateValues" dxfId="63" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="281" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="280" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="279" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="278" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="277" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="276" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="275" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F118:F133">
-    <cfRule type="duplicateValues" dxfId="56" priority="158"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="159"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="157"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="156"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="274" priority="162"/>
+    <cfRule type="duplicateValues" dxfId="273" priority="161"/>
+    <cfRule type="duplicateValues" dxfId="272" priority="159"/>
+    <cfRule type="duplicateValues" dxfId="271" priority="158"/>
+    <cfRule type="duplicateValues" dxfId="270" priority="160"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F134:F157 F2:F48 F74:F80 F101:F117">
-    <cfRule type="duplicateValues" dxfId="51" priority="164"/>
+    <cfRule type="duplicateValues" dxfId="269" priority="167"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F134:F157 F22:F48 F74:F80 F101:F117">
-    <cfRule type="duplicateValues" dxfId="50" priority="165"/>
+    <cfRule type="duplicateValues" dxfId="268" priority="168"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F158:F164">
-    <cfRule type="duplicateValues" dxfId="49" priority="143"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="144"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="145"/>
-    <cfRule type="containsText" dxfId="46" priority="147" operator="containsText" text="null">
+    <cfRule type="duplicateValues" dxfId="267" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="266" priority="148"/>
+    <cfRule type="duplicateValues" dxfId="265" priority="149"/>
+    <cfRule type="containsText" dxfId="264" priority="150" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",F158)))</formula>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="45" priority="146"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="148"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="142"/>
+    <cfRule type="duplicateValues" dxfId="263" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="262" priority="145"/>
+    <cfRule type="duplicateValues" dxfId="261" priority="146"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F165:F169">
-    <cfRule type="duplicateValues" dxfId="42" priority="123"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="124"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="125"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="122"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="121"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="260" priority="127"/>
+    <cfRule type="duplicateValues" dxfId="259" priority="128"/>
+    <cfRule type="duplicateValues" dxfId="258" priority="126"/>
+    <cfRule type="duplicateValues" dxfId="257" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="256" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="255" priority="124"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F173">
-    <cfRule type="duplicateValues" dxfId="36" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="254" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F174:F175 F171:F172">
-    <cfRule type="duplicateValues" dxfId="35" priority="198"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="197"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="196"/>
+    <cfRule type="duplicateValues" dxfId="253" priority="201"/>
+    <cfRule type="duplicateValues" dxfId="252" priority="200"/>
+    <cfRule type="duplicateValues" dxfId="251" priority="199"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F176 F183:F1048576 F1:F48 F74:F80 F101:F170">
-    <cfRule type="duplicateValues" dxfId="32" priority="118"/>
+  <conditionalFormatting sqref="F176 F187:F1048576 F1:F48 F74:F80 F101:F170">
+    <cfRule type="duplicateValues" dxfId="250" priority="121"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F177:F178 F180:F181">
-    <cfRule type="duplicateValues" dxfId="31" priority="76"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="78"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="249" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="248" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="247" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F177:F178">
-    <cfRule type="cellIs" dxfId="28" priority="75" operator="equal">
+    <cfRule type="cellIs" dxfId="246" priority="78" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F179">
-    <cfRule type="duplicateValues" dxfId="27" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="245" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F180:F181 E170 L170:Q181 T170:V181 E173 E174:F175 E176:E181">
-    <cfRule type="cellIs" dxfId="26" priority="115" operator="equal">
+    <cfRule type="cellIs" dxfId="244" priority="118" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F182">
-    <cfRule type="duplicateValues" dxfId="25" priority="3"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="L134:P156">
-    <cfRule type="cellIs" dxfId="24" priority="116" operator="equal">
+    <cfRule type="cellIs" dxfId="242" priority="119" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P21">
-    <cfRule type="cellIs" dxfId="23" priority="132" operator="equal">
+    <cfRule type="cellIs" dxfId="241" priority="135" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P128:P133">
-    <cfRule type="duplicateValues" dxfId="22" priority="126"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="127"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="128"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="130"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="129"/>
+    <cfRule type="duplicateValues" dxfId="240" priority="129"/>
+    <cfRule type="duplicateValues" dxfId="239" priority="130"/>
+    <cfRule type="duplicateValues" dxfId="238" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="237" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="236" priority="133"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R182">
-    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
+  <conditionalFormatting sqref="R1:R181">
+    <cfRule type="cellIs" dxfId="235" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y158:Y164">
-    <cfRule type="duplicateValues" dxfId="16" priority="141"/>
-    <cfRule type="containsText" dxfId="15" priority="140" operator="containsText" text="null">
+    <cfRule type="duplicateValues" dxfId="234" priority="144"/>
+    <cfRule type="containsText" dxfId="233" priority="143" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",Y158)))</formula>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="14" priority="139"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="138"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="137"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="136"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="135"/>
+    <cfRule type="duplicateValues" dxfId="232" priority="142"/>
+    <cfRule type="duplicateValues" dxfId="231" priority="141"/>
+    <cfRule type="duplicateValues" dxfId="230" priority="140"/>
+    <cfRule type="duplicateValues" dxfId="229" priority="139"/>
+    <cfRule type="duplicateValues" dxfId="228" priority="138"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y165:Y173">
-    <cfRule type="cellIs" dxfId="9" priority="80" operator="equal">
+  <conditionalFormatting sqref="Y165:Y169 Y173">
+    <cfRule type="cellIs" dxfId="227" priority="83" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y175:Y179 AA175:AA179">
-    <cfRule type="cellIs" dxfId="8" priority="14" operator="equal">
+  <conditionalFormatting sqref="Y175 Y179">
+    <cfRule type="cellIs" dxfId="226" priority="17" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y181 AA181">
-    <cfRule type="cellIs" dxfId="7" priority="59" operator="equal">
+  <conditionalFormatting sqref="Y181">
+    <cfRule type="cellIs" dxfId="225" priority="62" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y2:AA2 AB2:AB181 Y3:Y9 AA3:AA9 Z3:Z181">
-    <cfRule type="cellIs" dxfId="6" priority="51" operator="equal">
+  <conditionalFormatting sqref="Y2:Y9">
+    <cfRule type="cellIs" dxfId="224" priority="54" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA21">
-    <cfRule type="cellIs" dxfId="5" priority="131" operator="equal">
+  <conditionalFormatting sqref="AD2:XFD9 B2:B169 L22:P117 AD22:XFD117 Y29:Y157 D49:F49 AD134:XFD157 AD165:XFD169 AD171:XFD172 AD174:XFD175 AD179:XFD181">
+    <cfRule type="cellIs" dxfId="220" priority="22" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC2:AC133">
-    <cfRule type="cellIs" dxfId="4" priority="17" operator="equal">
+  <conditionalFormatting sqref="B182:B186">
+    <cfRule type="cellIs" dxfId="217" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC158:AC181">
-    <cfRule type="cellIs" dxfId="3" priority="16" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
+  <conditionalFormatting sqref="E186:F186">
+    <cfRule type="duplicateValues" dxfId="216" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD2:XFD9 B2:B169 L22:P117 AD22:XFD117 Y29:Y157 AA29:AA173 D49:F49 AC134:XFD157 AD165:XFD169 AD171:XFD172 AD174:XFD175 AD179:XFD181">
-    <cfRule type="cellIs" dxfId="2" priority="19" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
+  <conditionalFormatting sqref="F182:F185">
+    <cfRule type="duplicateValues" dxfId="215" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.51180555555555596" right="0.51180555555555596" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -23030,15 +25522,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="1.3046875" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="10" width="5.15234375" style="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="21" width="5.53515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="8"/>
+    <col min="1" max="1" width="1.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="10" width="5.140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="21" width="5.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="11.140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="15.45" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>12</v>
       </c>
@@ -23103,7 +25595,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -23178,14 +25670,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B299E44-CC41-4C47-93B0-FF411236635D}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="8.5" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.3828125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="3.69140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="6.69140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="6.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11">
         <v>1</v>
       </c>
@@ -23202,7 +25694,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="8.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="22">
         <v>2</v>
       </c>
@@ -23221,7 +25713,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="219" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23233,27 +25725,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96F4F343-F8A9-4565-8E75-460BD2B52D7E}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="7.4" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="7.35" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.69140625" style="55" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.53515625" style="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.3046875" style="34" customWidth="1"/>
-    <col min="4" max="4" width="2.3828125" style="34" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="1.84375" style="34" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="2.3828125" style="34" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="1.84375" style="34" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="2.3828125" style="34" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="1.84375" style="34" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="2.53515625" style="34" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.84375" style="34" customWidth="1"/>
-    <col min="12" max="12" width="2.3828125" style="34" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4.53515625" style="34" customWidth="1"/>
-    <col min="14" max="14" width="4.15234375" style="34" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.15234375" style="34" customWidth="1"/>
-    <col min="16" max="16384" width="9.3046875" style="34"/>
+    <col min="1" max="1" width="1.7109375" style="55" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.5703125" style="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" style="34" customWidth="1"/>
+    <col min="4" max="4" width="2.42578125" style="34" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="1.85546875" style="34" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="2.42578125" style="34" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="1.85546875" style="34" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="2.42578125" style="34" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="1.85546875" style="34" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="2.5703125" style="34" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.85546875" style="34" customWidth="1"/>
+    <col min="12" max="12" width="2.42578125" style="34" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.5703125" style="34" customWidth="1"/>
+    <col min="14" max="14" width="4.140625" style="34" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.140625" style="34" customWidth="1"/>
+    <col min="16" max="16384" width="9.28515625" style="34"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="20.7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:15" ht="20.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="53" t="s">
         <v>11</v>
       </c>
@@ -23300,7 +25792,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:15" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="54">
         <v>2</v>
       </c>
@@ -23350,7 +25842,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="218" priority="51"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Versão5/ARQ/Ontologia_Ambientes.xlsx
+++ b/Versão5/ARQ/Ontologia_Ambientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ARQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3176EF3-E449-4E98-A271-49461CE53A98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB2A5D6E-98C2-4537-B02B-D6676A049B5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3878" uniqueCount="946">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4064" uniqueCount="947">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -2909,6 +2909,9 @@
   </si>
   <si>
     <t>Defines a Code written in visual programming systems</t>
+  </si>
+  <si>
+    <t>KML</t>
   </si>
 </sst>
 </file>
@@ -3431,25 +3434,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="323">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="104">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3465,39 +3450,7 @@
         <b val="0"/>
         <i/>
         <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
+        <color rgb="FFFFFFFF"/>
       </font>
     </dxf>
     <dxf>
@@ -3584,6 +3537,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i/>
         <strike val="0"/>
@@ -3592,13 +3555,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3709,6 +3670,16 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -4460,2056 +4431,6 @@
         <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color rgb="FFFFFFFF"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -7116,7 +5037,7 @@
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46268.51108877315</v>
+        <v>46268.690614236111</v>
       </c>
       <c r="C18" s="39" t="s">
         <v>171</v>
@@ -7221,7 +5142,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC186"/>
+  <dimension ref="A1:AD186"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.140625" style="52" bestFit="1" customWidth="1"/>
@@ -7250,10 +5171,11 @@
     <col min="27" max="27" width="23.7109375" style="50" customWidth="1"/>
     <col min="28" max="28" width="6.85546875" style="50" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="15.85546875" style="61" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="36"/>
+    <col min="30" max="30" width="6.85546875" style="50" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="36"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="24" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" s="24" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="51">
         <v>0</v>
       </c>
@@ -7341,8 +5263,11 @@
       <c r="AC1" s="59" t="s">
         <v>921</v>
       </c>
+      <c r="AD1" s="26" t="s">
+        <v>946</v>
+      </c>
     </row>
-    <row r="2" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="49">
         <v>2</v>
       </c>
@@ -7438,8 +5363,11 @@
       <c r="AC2" s="56" t="s">
         <v>10</v>
       </c>
+      <c r="AD2" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="49">
         <v>3</v>
       </c>
@@ -7535,8 +5463,11 @@
       <c r="AC3" s="56" t="s">
         <v>10</v>
       </c>
+      <c r="AD3" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="4" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="49">
         <v>4</v>
       </c>
@@ -7632,8 +5563,11 @@
       <c r="AC4" s="56" t="s">
         <v>10</v>
       </c>
+      <c r="AD4" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="5" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="49">
         <v>5</v>
       </c>
@@ -7729,8 +5663,11 @@
       <c r="AC5" s="56" t="s">
         <v>10</v>
       </c>
+      <c r="AD5" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="6" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="49">
         <v>6</v>
       </c>
@@ -7826,8 +5763,11 @@
       <c r="AC6" s="56" t="s">
         <v>10</v>
       </c>
+      <c r="AD6" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="7" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="49">
         <v>7</v>
       </c>
@@ -7923,8 +5863,11 @@
       <c r="AC7" s="56" t="s">
         <v>10</v>
       </c>
+      <c r="AD7" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="8" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="49">
         <v>8</v>
       </c>
@@ -8020,8 +5963,11 @@
       <c r="AC8" s="56" t="s">
         <v>10</v>
       </c>
+      <c r="AD8" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="9" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="49">
         <v>9</v>
       </c>
@@ -8117,8 +6063,11 @@
       <c r="AC9" s="56" t="s">
         <v>10</v>
       </c>
+      <c r="AD9" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="10" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="49">
         <v>10</v>
       </c>
@@ -8214,8 +6163,11 @@
       <c r="AC10" s="56" t="s">
         <v>225</v>
       </c>
+      <c r="AD10" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="11" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="49">
         <v>11</v>
       </c>
@@ -8311,8 +6263,11 @@
       <c r="AC11" s="56" t="s">
         <v>225</v>
       </c>
+      <c r="AD11" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="12" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="49">
         <v>12</v>
       </c>
@@ -8408,8 +6363,11 @@
       <c r="AC12" s="56" t="s">
         <v>225</v>
       </c>
+      <c r="AD12" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="13" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="49">
         <v>13</v>
       </c>
@@ -8505,8 +6463,11 @@
       <c r="AC13" s="56" t="s">
         <v>225</v>
       </c>
+      <c r="AD13" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="14" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="49">
         <v>14</v>
       </c>
@@ -8602,8 +6563,11 @@
       <c r="AC14" s="56" t="s">
         <v>225</v>
       </c>
+      <c r="AD14" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="15" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="49">
         <v>15</v>
       </c>
@@ -8699,8 +6663,11 @@
       <c r="AC15" s="56" t="s">
         <v>225</v>
       </c>
+      <c r="AD15" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="16" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="49">
         <v>16</v>
       </c>
@@ -8796,8 +6763,11 @@
       <c r="AC16" s="56" t="s">
         <v>225</v>
       </c>
+      <c r="AD16" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="17" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="49">
         <v>17</v>
       </c>
@@ -8893,8 +6863,11 @@
       <c r="AC17" s="56" t="s">
         <v>225</v>
       </c>
+      <c r="AD17" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="18" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="49">
         <v>18</v>
       </c>
@@ -8990,8 +6963,11 @@
       <c r="AC18" s="56" t="s">
         <v>225</v>
       </c>
+      <c r="AD18" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="19" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="49">
         <v>19</v>
       </c>
@@ -9087,8 +7063,11 @@
       <c r="AC19" s="56" t="s">
         <v>225</v>
       </c>
+      <c r="AD19" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="20" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="49">
         <v>20</v>
       </c>
@@ -9184,8 +7163,11 @@
       <c r="AC20" s="56" t="s">
         <v>225</v>
       </c>
+      <c r="AD20" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="21" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="49">
         <v>21</v>
       </c>
@@ -9281,8 +7263,11 @@
       <c r="AC21" s="56" t="s">
         <v>225</v>
       </c>
+      <c r="AD21" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="22" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="49">
         <v>22</v>
       </c>
@@ -9378,8 +7363,11 @@
       <c r="AC22" s="56" t="s">
         <v>225</v>
       </c>
+      <c r="AD22" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="23" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="49">
         <v>23</v>
       </c>
@@ -9475,8 +7463,11 @@
       <c r="AC23" s="56" t="s">
         <v>225</v>
       </c>
+      <c r="AD23" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="24" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="49">
         <v>24</v>
       </c>
@@ -9572,8 +7563,11 @@
       <c r="AC24" s="56" t="s">
         <v>225</v>
       </c>
+      <c r="AD24" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="25" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="49">
         <v>25</v>
       </c>
@@ -9669,8 +7663,11 @@
       <c r="AC25" s="56" t="s">
         <v>225</v>
       </c>
+      <c r="AD25" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="26" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="49">
         <v>26</v>
       </c>
@@ -9766,8 +7763,11 @@
       <c r="AC26" s="56" t="s">
         <v>225</v>
       </c>
+      <c r="AD26" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="27" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="49">
         <v>27</v>
       </c>
@@ -9863,8 +7863,11 @@
       <c r="AC27" s="56" t="s">
         <v>225</v>
       </c>
+      <c r="AD27" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="28" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="49">
         <v>28</v>
       </c>
@@ -9960,8 +7963,11 @@
       <c r="AC28" s="56" t="s">
         <v>225</v>
       </c>
+      <c r="AD28" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="29" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="49">
         <v>29</v>
       </c>
@@ -10057,8 +8063,11 @@
       <c r="AC29" s="56" t="s">
         <v>10</v>
       </c>
+      <c r="AD29" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="30" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="49">
         <v>30</v>
       </c>
@@ -10154,8 +8163,11 @@
       <c r="AC30" s="56" t="s">
         <v>10</v>
       </c>
+      <c r="AD30" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="31" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="49">
         <v>31</v>
       </c>
@@ -10251,8 +8263,11 @@
       <c r="AC31" s="56" t="s">
         <v>10</v>
       </c>
+      <c r="AD31" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="32" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="49">
         <v>32</v>
       </c>
@@ -10348,8 +8363,11 @@
       <c r="AC32" s="56" t="s">
         <v>10</v>
       </c>
+      <c r="AD32" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="33" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="49">
         <v>33</v>
       </c>
@@ -10445,8 +8463,11 @@
       <c r="AC33" s="56" t="s">
         <v>10</v>
       </c>
+      <c r="AD33" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="34" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="49">
         <v>34</v>
       </c>
@@ -10542,8 +8563,11 @@
       <c r="AC34" s="56" t="s">
         <v>10</v>
       </c>
+      <c r="AD34" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="35" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="49">
         <v>35</v>
       </c>
@@ -10639,8 +8663,11 @@
       <c r="AC35" s="56" t="s">
         <v>356</v>
       </c>
+      <c r="AD35" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="36" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="49">
         <v>36</v>
       </c>
@@ -10736,8 +8763,11 @@
       <c r="AC36" s="56" t="s">
         <v>380</v>
       </c>
+      <c r="AD36" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="37" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="49">
         <v>37</v>
       </c>
@@ -10833,8 +8863,11 @@
       <c r="AC37" s="56" t="s">
         <v>379</v>
       </c>
+      <c r="AD37" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="38" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="49">
         <v>38</v>
       </c>
@@ -10930,8 +8963,11 @@
       <c r="AC38" s="56" t="s">
         <v>379</v>
       </c>
+      <c r="AD38" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="39" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="49">
         <v>39</v>
       </c>
@@ -11027,8 +9063,11 @@
       <c r="AC39" s="60" t="s">
         <v>377</v>
       </c>
+      <c r="AD39" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="40" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="49">
         <v>40</v>
       </c>
@@ -11124,8 +9163,11 @@
       <c r="AC40" s="60" t="s">
         <v>378</v>
       </c>
+      <c r="AD40" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="41" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="49">
         <v>41</v>
       </c>
@@ -11221,8 +9263,11 @@
       <c r="AC41" s="56" t="s">
         <v>355</v>
       </c>
+      <c r="AD41" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="42" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="49">
         <v>42</v>
       </c>
@@ -11318,8 +9363,11 @@
       <c r="AC42" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD42" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="43" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="49">
         <v>43</v>
       </c>
@@ -11415,8 +9463,11 @@
       <c r="AC43" s="56" t="s">
         <v>357</v>
       </c>
+      <c r="AD43" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="44" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="49">
         <v>44</v>
       </c>
@@ -11512,8 +9563,11 @@
       <c r="AC44" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD44" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="45" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="49">
         <v>45</v>
       </c>
@@ -11609,8 +9663,11 @@
       <c r="AC45" s="56" t="s">
         <v>358</v>
       </c>
+      <c r="AD45" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="46" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="49">
         <v>46</v>
       </c>
@@ -11706,8 +9763,11 @@
       <c r="AC46" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD46" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="47" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="49">
         <v>47</v>
       </c>
@@ -11803,8 +9863,11 @@
       <c r="AC47" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD47" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="48" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="49">
         <v>48</v>
       </c>
@@ -11900,8 +9963,11 @@
       <c r="AC48" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD48" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="49" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="49">
         <v>49</v>
       </c>
@@ -11997,8 +10063,11 @@
       <c r="AC49" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD49" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="50" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="49">
         <v>50</v>
       </c>
@@ -12094,8 +10163,11 @@
       <c r="AC50" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD50" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="51" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="49">
         <v>51</v>
       </c>
@@ -12191,8 +10263,11 @@
       <c r="AC51" s="56" t="s">
         <v>374</v>
       </c>
+      <c r="AD51" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="52" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="49">
         <v>52</v>
       </c>
@@ -12288,8 +10363,11 @@
       <c r="AC52" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD52" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="53" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="49">
         <v>53</v>
       </c>
@@ -12385,8 +10463,11 @@
       <c r="AC53" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD53" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="54" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="49">
         <v>54</v>
       </c>
@@ -12482,8 +10563,11 @@
       <c r="AC54" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD54" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="55" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="49">
         <v>55</v>
       </c>
@@ -12579,8 +10663,11 @@
       <c r="AC55" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD55" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="56" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="49">
         <v>56</v>
       </c>
@@ -12676,8 +10763,11 @@
       <c r="AC56" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD56" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="57" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="49">
         <v>57</v>
       </c>
@@ -12773,8 +10863,11 @@
       <c r="AC57" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD57" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="58" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="49">
         <v>58</v>
       </c>
@@ -12870,8 +10963,11 @@
       <c r="AC58" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD58" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="59" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="49">
         <v>59</v>
       </c>
@@ -12967,8 +11063,11 @@
       <c r="AC59" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD59" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="60" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="49">
         <v>60</v>
       </c>
@@ -13064,8 +11163,11 @@
       <c r="AC60" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD60" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="61" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="49">
         <v>61</v>
       </c>
@@ -13161,8 +11263,11 @@
       <c r="AC61" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD61" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="62" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="49">
         <v>62</v>
       </c>
@@ -13258,8 +11363,11 @@
       <c r="AC62" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD62" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="63" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="49">
         <v>63</v>
       </c>
@@ -13355,8 +11463,11 @@
       <c r="AC63" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD63" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="64" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="49">
         <v>64</v>
       </c>
@@ -13452,8 +11563,11 @@
       <c r="AC64" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD64" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="65" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="49">
         <v>65</v>
       </c>
@@ -13549,8 +11663,11 @@
       <c r="AC65" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD65" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="66" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="49">
         <v>66</v>
       </c>
@@ -13646,8 +11763,11 @@
       <c r="AC66" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD66" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="67" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="49">
         <v>67</v>
       </c>
@@ -13743,8 +11863,11 @@
       <c r="AC67" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD67" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="68" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="49">
         <v>68</v>
       </c>
@@ -13840,8 +11963,11 @@
       <c r="AC68" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD68" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="69" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="49">
         <v>69</v>
       </c>
@@ -13937,8 +12063,11 @@
       <c r="AC69" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD69" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="70" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="49">
         <v>70</v>
       </c>
@@ -14034,8 +12163,11 @@
       <c r="AC70" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD70" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="71" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="49">
         <v>71</v>
       </c>
@@ -14131,8 +12263,11 @@
       <c r="AC71" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD71" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="72" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="49">
         <v>72</v>
       </c>
@@ -14228,8 +12363,11 @@
       <c r="AC72" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD72" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="73" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="49">
         <v>73</v>
       </c>
@@ -14325,8 +12463,11 @@
       <c r="AC73" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD73" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="74" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="49">
         <v>74</v>
       </c>
@@ -14422,8 +12563,11 @@
       <c r="AC74" s="56" t="s">
         <v>226</v>
       </c>
+      <c r="AD74" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="75" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="49">
         <v>75</v>
       </c>
@@ -14519,8 +12663,11 @@
       <c r="AC75" s="56" t="s">
         <v>226</v>
       </c>
+      <c r="AD75" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="76" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="49">
         <v>76</v>
       </c>
@@ -14616,8 +12763,11 @@
       <c r="AC76" s="56" t="s">
         <v>226</v>
       </c>
+      <c r="AD76" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="77" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="49">
         <v>77</v>
       </c>
@@ -14713,8 +12863,11 @@
       <c r="AC77" s="56" t="s">
         <v>226</v>
       </c>
+      <c r="AD77" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="78" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="49">
         <v>78</v>
       </c>
@@ -14810,8 +12963,11 @@
       <c r="AC78" s="56" t="s">
         <v>226</v>
       </c>
+      <c r="AD78" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="79" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="49">
         <v>79</v>
       </c>
@@ -14907,8 +13063,11 @@
       <c r="AC79" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD79" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="80" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="49">
         <v>80</v>
       </c>
@@ -15004,8 +13163,11 @@
       <c r="AC80" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD80" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="81" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="49">
         <v>81</v>
       </c>
@@ -15101,8 +13263,11 @@
       <c r="AC81" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD81" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="82" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="49">
         <v>82</v>
       </c>
@@ -15198,8 +13363,11 @@
       <c r="AC82" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD82" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="83" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="49">
         <v>83</v>
       </c>
@@ -15295,8 +13463,11 @@
       <c r="AC83" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD83" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="84" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="49">
         <v>84</v>
       </c>
@@ -15392,8 +13563,11 @@
       <c r="AC84" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD84" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="85" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="49">
         <v>85</v>
       </c>
@@ -15489,8 +13663,11 @@
       <c r="AC85" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD85" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="86" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="49">
         <v>86</v>
       </c>
@@ -15586,8 +13763,11 @@
       <c r="AC86" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD86" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="87" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="49">
         <v>87</v>
       </c>
@@ -15683,8 +13863,11 @@
       <c r="AC87" s="56" t="s">
         <v>350</v>
       </c>
+      <c r="AD87" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="88" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="49">
         <v>88</v>
       </c>
@@ -15780,8 +13963,11 @@
       <c r="AC88" s="56" t="s">
         <v>350</v>
       </c>
+      <c r="AD88" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="89" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="49">
         <v>89</v>
       </c>
@@ -15877,8 +14063,11 @@
       <c r="AC89" s="56" t="s">
         <v>350</v>
       </c>
+      <c r="AD89" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="90" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="49">
         <v>90</v>
       </c>
@@ -15974,8 +14163,11 @@
       <c r="AC90" s="56" t="s">
         <v>350</v>
       </c>
+      <c r="AD90" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="91" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="49">
         <v>91</v>
       </c>
@@ -16071,8 +14263,11 @@
       <c r="AC91" s="56" t="s">
         <v>350</v>
       </c>
+      <c r="AD91" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="92" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="49">
         <v>92</v>
       </c>
@@ -16168,8 +14363,11 @@
       <c r="AC92" s="56" t="s">
         <v>350</v>
       </c>
+      <c r="AD92" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="93" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="49">
         <v>93</v>
       </c>
@@ -16265,8 +14463,11 @@
       <c r="AC93" s="56" t="s">
         <v>350</v>
       </c>
+      <c r="AD93" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="94" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="49">
         <v>94</v>
       </c>
@@ -16362,8 +14563,11 @@
       <c r="AC94" s="56" t="s">
         <v>350</v>
       </c>
+      <c r="AD94" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="95" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="49">
         <v>95</v>
       </c>
@@ -16459,8 +14663,11 @@
       <c r="AC95" s="56" t="s">
         <v>350</v>
       </c>
+      <c r="AD95" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="96" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="49">
         <v>96</v>
       </c>
@@ -16556,8 +14763,11 @@
       <c r="AC96" s="56" t="s">
         <v>350</v>
       </c>
+      <c r="AD96" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="97" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="49">
         <v>97</v>
       </c>
@@ -16653,8 +14863,11 @@
       <c r="AC97" s="56" t="s">
         <v>350</v>
       </c>
+      <c r="AD97" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="98" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="49">
         <v>98</v>
       </c>
@@ -16750,8 +14963,11 @@
       <c r="AC98" s="56" t="s">
         <v>350</v>
       </c>
+      <c r="AD98" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="99" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="49">
         <v>99</v>
       </c>
@@ -16847,8 +15063,11 @@
       <c r="AC99" s="56" t="s">
         <v>350</v>
       </c>
+      <c r="AD99" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="100" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="49">
         <v>100</v>
       </c>
@@ -16944,8 +15163,11 @@
       <c r="AC100" s="56" t="s">
         <v>350</v>
       </c>
+      <c r="AD100" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="101" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="49">
         <v>101</v>
       </c>
@@ -17041,8 +15263,11 @@
       <c r="AC101" s="56" t="s">
         <v>351</v>
       </c>
+      <c r="AD101" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="102" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="49">
         <v>102</v>
       </c>
@@ -17138,8 +15363,11 @@
       <c r="AC102" s="56" t="s">
         <v>351</v>
       </c>
+      <c r="AD102" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="103" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="49">
         <v>103</v>
       </c>
@@ -17235,8 +15463,11 @@
       <c r="AC103" s="56" t="s">
         <v>352</v>
       </c>
+      <c r="AD103" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="104" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="49">
         <v>104</v>
       </c>
@@ -17332,8 +15563,11 @@
       <c r="AC104" s="56" t="s">
         <v>351</v>
       </c>
+      <c r="AD104" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="105" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="49">
         <v>105</v>
       </c>
@@ -17429,8 +15663,11 @@
       <c r="AC105" s="56" t="s">
         <v>351</v>
       </c>
+      <c r="AD105" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="106" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="49">
         <v>106</v>
       </c>
@@ -17526,8 +15763,11 @@
       <c r="AC106" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD106" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="107" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="49">
         <v>107</v>
       </c>
@@ -17623,8 +15863,11 @@
       <c r="AC107" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD107" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="108" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="49">
         <v>108</v>
       </c>
@@ -17720,8 +15963,11 @@
       <c r="AC108" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD108" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="109" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="49">
         <v>109</v>
       </c>
@@ -17817,8 +16063,11 @@
       <c r="AC109" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD109" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="110" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="49">
         <v>110</v>
       </c>
@@ -17914,8 +16163,11 @@
       <c r="AC110" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD110" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="111" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="49">
         <v>111</v>
       </c>
@@ -18011,8 +16263,11 @@
       <c r="AC111" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD111" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="112" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="49">
         <v>112</v>
       </c>
@@ -18108,8 +16363,11 @@
       <c r="AC112" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD112" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="113" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="49">
         <v>113</v>
       </c>
@@ -18205,8 +16463,11 @@
       <c r="AC113" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD113" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="114" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="49">
         <v>114</v>
       </c>
@@ -18302,8 +16563,11 @@
       <c r="AC114" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD114" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="115" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="49">
         <v>115</v>
       </c>
@@ -18399,8 +16663,11 @@
       <c r="AC115" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD115" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="116" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="49">
         <v>116</v>
       </c>
@@ -18496,8 +16763,11 @@
       <c r="AC116" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD116" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="117" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="49">
         <v>117</v>
       </c>
@@ -18593,8 +16863,11 @@
       <c r="AC117" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD117" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="118" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="49">
         <v>118</v>
       </c>
@@ -18690,8 +16963,11 @@
       <c r="AC118" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD118" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="119" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="49">
         <v>119</v>
       </c>
@@ -18787,8 +17063,11 @@
       <c r="AC119" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD119" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="120" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="49">
         <v>120</v>
       </c>
@@ -18884,8 +17163,11 @@
       <c r="AC120" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD120" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="121" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="49">
         <v>121</v>
       </c>
@@ -18981,8 +17263,11 @@
       <c r="AC121" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD121" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="122" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="49">
         <v>122</v>
       </c>
@@ -19078,8 +17363,11 @@
       <c r="AC122" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD122" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="123" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="49">
         <v>123</v>
       </c>
@@ -19175,8 +17463,11 @@
       <c r="AC123" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD123" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="124" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="49">
         <v>124</v>
       </c>
@@ -19272,8 +17563,11 @@
       <c r="AC124" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD124" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="125" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="49">
         <v>125</v>
       </c>
@@ -19369,8 +17663,11 @@
       <c r="AC125" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD125" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="126" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="49">
         <v>126</v>
       </c>
@@ -19466,8 +17763,11 @@
       <c r="AC126" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD126" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="127" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="49">
         <v>127</v>
       </c>
@@ -19563,8 +17863,11 @@
       <c r="AC127" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD127" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="128" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="49">
         <v>128</v>
       </c>
@@ -19660,8 +17963,11 @@
       <c r="AC128" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD128" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="129" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="49">
         <v>129</v>
       </c>
@@ -19757,8 +18063,11 @@
       <c r="AC129" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD129" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="130" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="49">
         <v>130</v>
       </c>
@@ -19854,8 +18163,11 @@
       <c r="AC130" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD130" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="131" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="49">
         <v>131</v>
       </c>
@@ -19951,8 +18263,11 @@
       <c r="AC131" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD131" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="132" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="49">
         <v>132</v>
       </c>
@@ -20048,8 +18363,11 @@
       <c r="AC132" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD132" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="133" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="49">
         <v>133</v>
       </c>
@@ -20145,8 +18463,11 @@
       <c r="AC133" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD133" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="134" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="49">
         <v>134</v>
       </c>
@@ -20242,8 +18563,11 @@
       <c r="AC134" s="56" t="s">
         <v>552</v>
       </c>
+      <c r="AD134" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="135" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="49">
         <v>135</v>
       </c>
@@ -20339,8 +18663,11 @@
       <c r="AC135" s="56" t="s">
         <v>552</v>
       </c>
+      <c r="AD135" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="136" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="49">
         <v>136</v>
       </c>
@@ -20436,8 +18763,11 @@
       <c r="AC136" s="56" t="s">
         <v>552</v>
       </c>
+      <c r="AD136" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="137" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="49">
         <v>137</v>
       </c>
@@ -20533,8 +18863,11 @@
       <c r="AC137" s="56" t="s">
         <v>552</v>
       </c>
+      <c r="AD137" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="138" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="49">
         <v>138</v>
       </c>
@@ -20630,8 +18963,11 @@
       <c r="AC138" s="56" t="s">
         <v>552</v>
       </c>
+      <c r="AD138" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="139" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="49">
         <v>139</v>
       </c>
@@ -20727,8 +19063,11 @@
       <c r="AC139" s="56" t="s">
         <v>224</v>
       </c>
+      <c r="AD139" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="140" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="49">
         <v>140</v>
       </c>
@@ -20824,8 +19163,11 @@
       <c r="AC140" s="56" t="s">
         <v>224</v>
       </c>
+      <c r="AD140" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="141" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="49">
         <v>141</v>
       </c>
@@ -20921,8 +19263,11 @@
       <c r="AC141" s="56" t="s">
         <v>223</v>
       </c>
+      <c r="AD141" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="142" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="49">
         <v>142</v>
       </c>
@@ -21018,8 +19363,11 @@
       <c r="AC142" s="56" t="s">
         <v>221</v>
       </c>
+      <c r="AD142" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="143" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="49">
         <v>143</v>
       </c>
@@ -21115,8 +19463,11 @@
       <c r="AC143" s="56" t="s">
         <v>222</v>
       </c>
+      <c r="AD143" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="144" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="49">
         <v>144</v>
       </c>
@@ -21212,8 +19563,11 @@
       <c r="AC144" s="56" t="s">
         <v>222</v>
       </c>
+      <c r="AD144" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="145" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="49">
         <v>145</v>
       </c>
@@ -21309,8 +19663,11 @@
       <c r="AC145" s="56" t="s">
         <v>222</v>
       </c>
+      <c r="AD145" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="146" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="49">
         <v>146</v>
       </c>
@@ -21406,8 +19763,11 @@
       <c r="AC146" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD146" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="147" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="49">
         <v>147</v>
       </c>
@@ -21503,8 +19863,11 @@
       <c r="AC147" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD147" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="148" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="49">
         <v>148</v>
       </c>
@@ -21600,8 +19963,11 @@
       <c r="AC148" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD148" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="149" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="49">
         <v>149</v>
       </c>
@@ -21697,8 +20063,11 @@
       <c r="AC149" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD149" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="150" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="49">
         <v>150</v>
       </c>
@@ -21794,8 +20163,11 @@
       <c r="AC150" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD150" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="151" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="49">
         <v>151</v>
       </c>
@@ -21891,8 +20263,11 @@
       <c r="AC151" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD151" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="152" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="49">
         <v>152</v>
       </c>
@@ -21988,8 +20363,11 @@
       <c r="AC152" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD152" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="153" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="49">
         <v>153</v>
       </c>
@@ -22085,8 +20463,11 @@
       <c r="AC153" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD153" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="154" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="49">
         <v>154</v>
       </c>
@@ -22182,8 +20563,11 @@
       <c r="AC154" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD154" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="155" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="49">
         <v>155</v>
       </c>
@@ -22279,8 +20663,11 @@
       <c r="AC155" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD155" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="156" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="49">
         <v>156</v>
       </c>
@@ -22376,8 +20763,11 @@
       <c r="AC156" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD156" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="157" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="49">
         <v>157</v>
       </c>
@@ -22473,8 +20863,11 @@
       <c r="AC157" s="56" t="s">
         <v>551</v>
       </c>
+      <c r="AD157" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="158" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="49">
         <v>158</v>
       </c>
@@ -22570,8 +20963,11 @@
       <c r="AC158" s="56" t="s">
         <v>10</v>
       </c>
+      <c r="AD158" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="159" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="49">
         <v>159</v>
       </c>
@@ -22667,8 +21063,11 @@
       <c r="AC159" s="56" t="s">
         <v>10</v>
       </c>
+      <c r="AD159" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="160" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="49">
         <v>160</v>
       </c>
@@ -22764,8 +21163,11 @@
       <c r="AC160" s="56" t="s">
         <v>10</v>
       </c>
+      <c r="AD160" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="161" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="49">
         <v>161</v>
       </c>
@@ -22861,8 +21263,11 @@
       <c r="AC161" s="56" t="s">
         <v>10</v>
       </c>
+      <c r="AD161" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="162" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="49">
         <v>162</v>
       </c>
@@ -22958,8 +21363,11 @@
       <c r="AC162" s="56" t="s">
         <v>10</v>
       </c>
+      <c r="AD162" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="163" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="49">
         <v>163</v>
       </c>
@@ -23055,8 +21463,11 @@
       <c r="AC163" s="56" t="s">
         <v>10</v>
       </c>
+      <c r="AD163" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="164" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="49">
         <v>164</v>
       </c>
@@ -23152,8 +21563,11 @@
       <c r="AC164" s="56" t="s">
         <v>10</v>
       </c>
+      <c r="AD164" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="165" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="49">
         <v>165</v>
       </c>
@@ -23249,8 +21663,11 @@
       <c r="AC165" s="56" t="s">
         <v>10</v>
       </c>
+      <c r="AD165" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="166" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="49">
         <v>166</v>
       </c>
@@ -23346,8 +21763,11 @@
       <c r="AC166" s="56" t="s">
         <v>10</v>
       </c>
+      <c r="AD166" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="167" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="49">
         <v>167</v>
       </c>
@@ -23443,8 +21863,11 @@
       <c r="AC167" s="56" t="s">
         <v>10</v>
       </c>
+      <c r="AD167" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="168" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="49">
         <v>168</v>
       </c>
@@ -23540,8 +21963,11 @@
       <c r="AC168" s="56" t="s">
         <v>10</v>
       </c>
+      <c r="AD168" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="169" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="49">
         <v>169</v>
       </c>
@@ -23637,8 +22063,11 @@
       <c r="AC169" s="56" t="s">
         <v>10</v>
       </c>
+      <c r="AD169" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="170" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="49">
         <v>170</v>
       </c>
@@ -23734,8 +22163,11 @@
       <c r="AC170" s="56" t="s">
         <v>10</v>
       </c>
+      <c r="AD170" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="171" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="49">
         <v>171</v>
       </c>
@@ -23831,8 +22263,11 @@
       <c r="AC171" s="56" t="s">
         <v>10</v>
       </c>
+      <c r="AD171" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="172" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="49">
         <v>172</v>
       </c>
@@ -23928,8 +22363,11 @@
       <c r="AC172" s="56" t="s">
         <v>10</v>
       </c>
+      <c r="AD172" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="173" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="49">
         <v>173</v>
       </c>
@@ -24025,8 +22463,11 @@
       <c r="AC173" s="56" t="s">
         <v>10</v>
       </c>
+      <c r="AD173" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="174" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="49">
         <v>174</v>
       </c>
@@ -24122,8 +22563,11 @@
       <c r="AC174" s="56" t="s">
         <v>225</v>
       </c>
+      <c r="AD174" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="175" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="49">
         <v>175</v>
       </c>
@@ -24219,8 +22663,11 @@
       <c r="AC175" s="56" t="s">
         <v>350</v>
       </c>
+      <c r="AD175" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="176" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="49">
         <v>176</v>
       </c>
@@ -24316,8 +22763,11 @@
       <c r="AC176" s="56" t="s">
         <v>10</v>
       </c>
+      <c r="AD176" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="177" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="49">
         <v>177</v>
       </c>
@@ -24413,8 +22863,11 @@
       <c r="AC177" s="56" t="s">
         <v>10</v>
       </c>
+      <c r="AD177" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="178" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="49">
         <v>178</v>
       </c>
@@ -24510,8 +22963,11 @@
       <c r="AC178" s="56" t="s">
         <v>10</v>
       </c>
+      <c r="AD178" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="179" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:30" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="49">
         <v>179</v>
       </c>
@@ -24607,8 +23063,11 @@
       <c r="AC179" s="56" t="s">
         <v>10</v>
       </c>
+      <c r="AD179" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="180" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="49">
         <v>180</v>
       </c>
@@ -24704,8 +23163,11 @@
       <c r="AC180" s="56" t="s">
         <v>225</v>
       </c>
+      <c r="AD180" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="181" spans="1:29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:30" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="49">
         <v>181</v>
       </c>
@@ -24801,8 +23263,11 @@
       <c r="AC181" s="56" t="s">
         <v>350</v>
       </c>
+      <c r="AD181" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="182" spans="1:29" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="49">
         <v>182</v>
       </c>
@@ -24898,8 +23363,11 @@
       <c r="AC182" s="63" t="s">
         <v>10</v>
       </c>
+      <c r="AD182" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="183" spans="1:29" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="49">
         <v>183</v>
       </c>
@@ -24995,8 +23463,11 @@
       <c r="AC183" s="63" t="s">
         <v>10</v>
       </c>
+      <c r="AD183" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="184" spans="1:29" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="49">
         <v>184</v>
       </c>
@@ -25092,8 +23563,11 @@
       <c r="AC184" s="63" t="s">
         <v>10</v>
       </c>
+      <c r="AD184" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="185" spans="1:29" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="49">
         <v>185</v>
       </c>
@@ -25189,8 +23663,11 @@
       <c r="AC185" s="63" t="s">
         <v>10</v>
       </c>
+      <c r="AD185" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="186" spans="1:29" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="49">
         <v>186</v>
       </c>
@@ -25286,232 +23763,235 @@
       <c r="AC186" s="63" t="s">
         <v>10</v>
       </c>
+      <c r="AD186" s="63" t="s">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="B182:B186">
+    <cfRule type="cellIs" dxfId="103" priority="1" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B170:D181">
-    <cfRule type="cellIs" dxfId="321" priority="63" operator="equal">
+    <cfRule type="cellIs" dxfId="102" priority="63" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:F9 L2:P9">
-    <cfRule type="cellIs" dxfId="320" priority="55" operator="equal">
+    <cfRule type="cellIs" dxfId="101" priority="55" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D50:F73">
-    <cfRule type="cellIs" dxfId="319" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="100" priority="40" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D81:F86">
-    <cfRule type="cellIs" dxfId="318" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="99" priority="32" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D87:F100">
-    <cfRule type="cellIs" dxfId="317" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="98" priority="24" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E22:F28 D29:F48 D74:F80 E101:F117 D134:F157 D101:D133 K157:P157 A2:A186">
-    <cfRule type="cellIs" dxfId="0" priority="157" operator="equal">
+  <conditionalFormatting sqref="E22:F28 D29:F48 D74:F80 E101:F117 D134:F157 A2:A186 D101:D133 K157:P157">
+    <cfRule type="cellIs" dxfId="97" priority="157" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E165:F169 L158:O164 L165:P169">
-    <cfRule type="cellIs" dxfId="316" priority="136" operator="equal">
+    <cfRule type="cellIs" dxfId="96" priority="136" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E171:F172">
-    <cfRule type="cellIs" dxfId="315" priority="73" operator="equal">
+    <cfRule type="cellIs" dxfId="95" priority="73" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E186:F186">
+    <cfRule type="duplicateValues" dxfId="94" priority="2"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F2:F9">
-    <cfRule type="duplicateValues" dxfId="314" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="313" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="312" priority="58"/>
-    <cfRule type="duplicateValues" dxfId="311" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="310" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F10:F21">
-    <cfRule type="duplicateValues" dxfId="309" priority="152"/>
-    <cfRule type="duplicateValues" dxfId="308" priority="153"/>
-    <cfRule type="duplicateValues" dxfId="307" priority="155"/>
-    <cfRule type="duplicateValues" dxfId="306" priority="156"/>
-    <cfRule type="duplicateValues" dxfId="305" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="156"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="152"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F49:F67">
-    <cfRule type="duplicateValues" dxfId="304" priority="300"/>
-    <cfRule type="duplicateValues" dxfId="303" priority="298"/>
-    <cfRule type="duplicateValues" dxfId="302" priority="301"/>
-    <cfRule type="duplicateValues" dxfId="301" priority="302"/>
-    <cfRule type="duplicateValues" dxfId="300" priority="303"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="303"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="302"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="301"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="300"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="298"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F68:F73">
-    <cfRule type="duplicateValues" dxfId="299" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="298" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="297" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="296" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="295" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="294" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="293" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F74:F80 F22:F48 F101:F117">
-    <cfRule type="duplicateValues" dxfId="292" priority="270"/>
-    <cfRule type="duplicateValues" dxfId="291" priority="271"/>
-    <cfRule type="duplicateValues" dxfId="290" priority="272"/>
-    <cfRule type="duplicateValues" dxfId="289" priority="273"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="270"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="273"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="272"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="271"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F81:F86">
-    <cfRule type="duplicateValues" dxfId="288" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="287" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="286" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="285" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="284" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="283" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="282" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F87:F100">
-    <cfRule type="duplicateValues" dxfId="281" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="280" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="279" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="278" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="277" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="276" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="275" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F118:F133">
-    <cfRule type="duplicateValues" dxfId="274" priority="162"/>
-    <cfRule type="duplicateValues" dxfId="273" priority="161"/>
-    <cfRule type="duplicateValues" dxfId="272" priority="159"/>
-    <cfRule type="duplicateValues" dxfId="271" priority="158"/>
-    <cfRule type="duplicateValues" dxfId="270" priority="160"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="161"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="162"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="160"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="158"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="159"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F134:F157 F2:F48 F74:F80 F101:F117">
-    <cfRule type="duplicateValues" dxfId="269" priority="167"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="167"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F134:F157 F22:F48 F74:F80 F101:F117">
-    <cfRule type="duplicateValues" dxfId="268" priority="168"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="168"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F158:F164">
-    <cfRule type="duplicateValues" dxfId="267" priority="147"/>
-    <cfRule type="duplicateValues" dxfId="266" priority="148"/>
-    <cfRule type="duplicateValues" dxfId="265" priority="149"/>
-    <cfRule type="containsText" dxfId="264" priority="150" operator="containsText" text="null">
+    <cfRule type="duplicateValues" dxfId="46" priority="146"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="145"/>
+    <cfRule type="containsText" dxfId="44" priority="150" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",F158)))</formula>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="263" priority="151"/>
-    <cfRule type="duplicateValues" dxfId="262" priority="145"/>
-    <cfRule type="duplicateValues" dxfId="261" priority="146"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="148"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="151"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F165:F169">
-    <cfRule type="duplicateValues" dxfId="260" priority="127"/>
-    <cfRule type="duplicateValues" dxfId="259" priority="128"/>
-    <cfRule type="duplicateValues" dxfId="258" priority="126"/>
-    <cfRule type="duplicateValues" dxfId="257" priority="123"/>
-    <cfRule type="duplicateValues" dxfId="256" priority="125"/>
-    <cfRule type="duplicateValues" dxfId="255" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="126"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="127"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="128"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="123"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F173">
-    <cfRule type="duplicateValues" dxfId="254" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F174:F175 F171:F172">
-    <cfRule type="duplicateValues" dxfId="253" priority="201"/>
-    <cfRule type="duplicateValues" dxfId="252" priority="200"/>
-    <cfRule type="duplicateValues" dxfId="251" priority="199"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="201"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="199"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="200"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F176 F187:F1048576 F1:F48 F74:F80 F101:F170">
-    <cfRule type="duplicateValues" dxfId="250" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="121"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F177:F178 F180:F181">
-    <cfRule type="duplicateValues" dxfId="249" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="248" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="247" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F177:F178">
-    <cfRule type="cellIs" dxfId="246" priority="78" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="78" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F179">
-    <cfRule type="duplicateValues" dxfId="245" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F180:F181 E170 L170:Q181 T170:V181 E173 E174:F175 E176:E181">
-    <cfRule type="cellIs" dxfId="244" priority="118" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="118" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F182:F185">
+    <cfRule type="duplicateValues" dxfId="22" priority="3"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L134:P156">
-    <cfRule type="cellIs" dxfId="242" priority="119" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="119" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P21">
-    <cfRule type="cellIs" dxfId="241" priority="135" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="135" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P128:P133">
-    <cfRule type="duplicateValues" dxfId="240" priority="129"/>
-    <cfRule type="duplicateValues" dxfId="239" priority="130"/>
-    <cfRule type="duplicateValues" dxfId="238" priority="131"/>
-    <cfRule type="duplicateValues" dxfId="237" priority="132"/>
-    <cfRule type="duplicateValues" dxfId="236" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="130"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="129"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="133"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R181">
-    <cfRule type="cellIs" dxfId="235" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="4" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y2:Y9">
+    <cfRule type="cellIs" dxfId="13" priority="54" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y158:Y164">
-    <cfRule type="duplicateValues" dxfId="234" priority="144"/>
-    <cfRule type="containsText" dxfId="233" priority="143" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="12" priority="143" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",Y158)))</formula>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="232" priority="142"/>
-    <cfRule type="duplicateValues" dxfId="231" priority="141"/>
-    <cfRule type="duplicateValues" dxfId="230" priority="140"/>
-    <cfRule type="duplicateValues" dxfId="229" priority="139"/>
-    <cfRule type="duplicateValues" dxfId="228" priority="138"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="144"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="141"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="140"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="139"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="142"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="138"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y165:Y169 Y173">
-    <cfRule type="cellIs" dxfId="227" priority="83" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="83" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y175 Y179">
-    <cfRule type="cellIs" dxfId="226" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="17" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y181">
-    <cfRule type="cellIs" dxfId="225" priority="62" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="62" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y2:Y9">
-    <cfRule type="cellIs" dxfId="224" priority="54" operator="equal">
+  <conditionalFormatting sqref="AE2:XFD9 B2:B169 L22:P117 AE22:XFD117 Y29:Y157 D49:F49 AE134:XFD157 AE165:XFD169 AE171:XFD172 AE174:XFD175 AE179:XFD181">
+    <cfRule type="cellIs" dxfId="2" priority="22" operator="equal">
       <formula>"null"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD2:XFD9 B2:B169 L22:P117 AD22:XFD117 Y29:Y157 D49:F49 AD134:XFD157 AD165:XFD169 AD171:XFD172 AD174:XFD175 AD179:XFD181">
-    <cfRule type="cellIs" dxfId="220" priority="22" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B182:B186">
-    <cfRule type="cellIs" dxfId="217" priority="1" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E186:F186">
-    <cfRule type="duplicateValues" dxfId="216" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F182:F185">
-    <cfRule type="duplicateValues" dxfId="215" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.51180555555555596" right="0.51180555555555596" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -25713,7 +24193,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
-    <cfRule type="cellIs" dxfId="219" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25842,7 +24322,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="218" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="51"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
